--- a/kinds_Listen_Origin.xlsx
+++ b/kinds_Listen_Origin.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mục lục" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL.md" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="110001" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="110002" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="110003" sheetId="5" state="visible" r:id="rId5"/>
@@ -545,6 +545,8 @@
           <t>Danh sách nội dung — Listen_Origin</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -894,6 +896,11 @@
           <t>Kind: 110008</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -901,6 +908,11 @@
           <t>KIND 110008 — DEPRECATED</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -982,6 +994,11 @@
           <t>Kind: 110008_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -989,6 +1006,11 @@
           <t>KIND 110008_1 — Hội thoại ngắn [25~30] (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -996,6 +1018,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1183,6 +1210,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -1360,6 +1392,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -1403,6 +1440,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -1424,6 +1466,11 @@
           <t>Cấu trúc đáp án — 2 câu hỏi con</t>
         </is>
       </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
@@ -1553,6 +1600,11 @@
           <t>Kind: 110008_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -1560,6 +1612,11 @@
           <t>KIND 110008_2 — Hội thoại ngắn [25~30] (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -1567,6 +1624,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1754,6 +1816,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -1931,6 +1998,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -1974,6 +2046,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -1995,6 +2072,11 @@
           <t>Cấu trúc đáp án — 2 câu hỏi con</t>
         </is>
       </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
@@ -2124,6 +2206,11 @@
           <t>Kind: 110008_3</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -2131,6 +2218,11 @@
           <t>KIND 110008_3 — Hội thoại ngắn [25~30] (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -2138,6 +2230,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -2325,6 +2422,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -2502,6 +2604,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -2545,6 +2652,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -2566,6 +2678,11 @@
           <t>Cấu trúc đáp án — 2 câu hỏi con</t>
         </is>
       </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
@@ -2695,6 +2812,11 @@
           <t>Kind: 210001_1</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -2702,6 +2824,11 @@
           <t>KIND 210001_1 — Chọn hình phù hợp (TOPIK II, Level 2) [ẢNH]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -2709,6 +2836,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -2824,6 +2956,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -2999,6 +3136,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -3013,6 +3155,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -3056,6 +3203,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -3070,6 +3222,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -3098,6 +3255,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -3133,6 +3295,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -3147,6 +3314,11 @@
           <t>Quy tắc tạo 4 bức tranh</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -3182,6 +3354,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -3343,6 +3520,11 @@
           <t>Kind: 210001_2</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -3350,6 +3532,11 @@
           <t>KIND 210001_2 — Chọn biểu đồ phù hợp (TOPIK II, Level 2) [ẢNH]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -3357,6 +3544,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -3472,6 +3664,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -3643,6 +3840,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -3657,6 +3859,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -3700,6 +3907,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -3714,6 +3926,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -3742,6 +3959,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -3777,6 +3999,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -3791,6 +4018,11 @@
           <t>Quy tắc tạo 4 biểu đồ</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -3826,6 +4058,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -3987,6 +4224,11 @@
           <t>Kind: 210002</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -3994,6 +4236,11 @@
           <t>KIND 210002 — Câu nối tiếp nâng cao (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -4001,6 +4248,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -4104,6 +4356,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -4279,6 +4536,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -4293,6 +4555,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -4336,6 +4603,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -4411,6 +4683,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -4446,6 +4723,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -4481,6 +4763,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -4509,6 +4796,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -4619,6 +4911,11 @@
           <t>Kind: 210003</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -4626,6 +4923,11 @@
           <t>KIND 210003 — Dự đoán hành động (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -4633,6 +4935,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -4736,6 +5043,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -4911,6 +5223,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -4925,6 +5242,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -4980,6 +5302,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -5072,6 +5399,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -5100,6 +5432,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -5135,6 +5472,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -5170,6 +5512,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -5280,6 +5627,11 @@
           <t>Kind: 210004</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -5287,6 +5639,11 @@
           <t>KIND 210004 — Khớp nội dung nâng cao (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -5294,6 +5651,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -5397,6 +5759,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -5572,6 +5939,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -5586,6 +5958,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -5641,6 +6018,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -5740,6 +6122,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -5768,6 +6155,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -5803,6 +6195,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -5838,6 +6235,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -5949,6 +6351,11 @@
           <t>Kind: 210005</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -5956,6 +6363,11 @@
           <t>KIND 210005 — Ý chính của nam (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -5963,6 +6375,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -6066,6 +6483,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -6241,6 +6663,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -6255,6 +6682,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -6310,6 +6742,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -6409,6 +6846,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -6437,6 +6879,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -6465,6 +6912,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -6507,6 +6959,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -6618,6 +7075,11 @@
           <t>SKILL.md — Listen_Origin</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -6625,6 +7087,11 @@
           <t>TOPIK Listening Question Generator (TOPIK I &amp; II)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -6639,6 +7106,11 @@
           <t>Khi nào dùng skill này</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -6667,6 +7139,11 @@
           <t>Cấu trúc thư mục</t>
         </is>
       </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -6856,6 +7333,11 @@
           <t>Output Format (JSON)</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -7227,6 +7709,11 @@
           <t>Danh mục chủ đề (topic)</t>
         </is>
       </c>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="10" t="n"/>
+      <c r="F92" s="10" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -7628,6 +8115,11 @@
           <t>Chiến lược bẫy đáp án sai (distractor_trap)</t>
         </is>
       </c>
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="10" t="n"/>
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="10" t="n"/>
+      <c r="F116" s="10" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
@@ -8035,6 +8527,11 @@
           <t>Đặc điểm câu hỏi (question_feature)</t>
         </is>
       </c>
+      <c r="B146" s="10" t="n"/>
+      <c r="C146" s="10" t="n"/>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="10" t="n"/>
+      <c r="F146" s="10" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
@@ -8555,6 +9052,11 @@
           <t>Cấu trúc ngữ pháp trong audio (grammar_semantic)</t>
         </is>
       </c>
+      <c r="B178" s="10" t="n"/>
+      <c r="C178" s="10" t="n"/>
+      <c r="D178" s="10" t="n"/>
+      <c r="E178" s="10" t="n"/>
+      <c r="F178" s="10" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
@@ -9294,6 +9796,11 @@
           <t>Cấu trúc audio (audio_format)</t>
         </is>
       </c>
+      <c r="B217" s="10" t="n"/>
+      <c r="C217" s="10" t="n"/>
+      <c r="D217" s="10" t="n"/>
+      <c r="E217" s="10" t="n"/>
+      <c r="F217" s="10" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="14" t="inlineStr">
@@ -9440,6 +9947,11 @@
           <t>Thang độ khó (Difficulty Scale)</t>
         </is>
       </c>
+      <c r="B226" s="10" t="n"/>
+      <c r="C226" s="10" t="n"/>
+      <c r="D226" s="10" t="n"/>
+      <c r="E226" s="10" t="n"/>
+      <c r="F226" s="10" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="14" t="inlineStr">
@@ -9803,6 +10315,11 @@
           <t>Cấp độ giao tiếp trong audio (speech_level)</t>
         </is>
       </c>
+      <c r="B252" s="10" t="n"/>
+      <c r="C252" s="10" t="n"/>
+      <c r="D252" s="10" t="n"/>
+      <c r="E252" s="10" t="n"/>
+      <c r="F252" s="10" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
@@ -9882,6 +10399,11 @@
           <t>Quy tắc chung khi gen câu hỏi</t>
         </is>
       </c>
+      <c r="B260" s="10" t="n"/>
+      <c r="C260" s="10" t="n"/>
+      <c r="D260" s="10" t="n"/>
+      <c r="E260" s="10" t="n"/>
+      <c r="F260" s="10" t="n"/>
     </row>
     <row r="261" ht="22" customHeight="1">
       <c r="A261" s="13" t="inlineStr">
@@ -10064,6 +10586,11 @@
           <t>Workflow</t>
         </is>
       </c>
+      <c r="B286" s="10" t="n"/>
+      <c r="C286" s="10" t="n"/>
+      <c r="D286" s="10" t="n"/>
+      <c r="E286" s="10" t="n"/>
+      <c r="F286" s="10" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
@@ -10208,8 +10735,8 @@
     <mergeCell ref="A266:F266"/>
     <mergeCell ref="A291:F291"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A124:F124"/>
     <mergeCell ref="A237:F237"/>
-    <mergeCell ref="A124:F124"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
@@ -10365,6 +10892,11 @@
           <t>Kind: 210006</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -10372,6 +10904,11 @@
           <t>KIND 210006 — 2 câu hỏi / hội thoại (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -10379,6 +10916,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -10482,6 +11024,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -10673,6 +11220,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -10687,6 +11239,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -10730,6 +11287,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -10829,6 +11391,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -10857,6 +11424,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -11012,6 +11584,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -11061,6 +11638,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
@@ -11408,13 +11990,12 @@
     <mergeCell ref="A105:F105"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
     <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A87:F87"/>
     <mergeCell ref="A95:F95"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="A71:F71"/>
@@ -11443,6 +12024,7 @@
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A124:F124"/>
     <mergeCell ref="A111:F111"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A48:F48"/>
@@ -11467,7 +12049,7 @@
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A88:F88"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11497,6 +12079,11 @@
           <t>Kind: 210007</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -11504,6 +12091,11 @@
           <t>KIND 210007 — Chương trình giáo dục / Tọa đàm (TOPIK II, Level 2)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -11511,6 +12103,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -11614,6 +12211,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -11821,6 +12423,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -11835,6 +12442,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -11878,6 +12490,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -11977,6 +12594,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -12012,6 +12634,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -12131,6 +12758,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -12180,6 +12812,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
@@ -12620,6 +13257,11 @@
           <t>Kind: 110001</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -12627,6 +13269,11 @@
           <t>KIND 110001 — Hỏi-đáp đơn giản (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -12634,6 +13281,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -12737,6 +13389,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -12912,6 +13569,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -12926,6 +13588,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -12981,6 +13648,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -13056,6 +13728,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -13084,6 +13761,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -13119,6 +13801,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -13208,6 +13895,11 @@
           <t>Kind: 110002</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -13215,6 +13907,11 @@
           <t>KIND 110002 — Chọn câu nối tiếp (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -13222,6 +13919,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -13325,6 +14027,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -13500,6 +14207,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -13514,6 +14226,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -13557,6 +14274,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -13615,6 +14337,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -13643,6 +14370,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -13678,6 +14410,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -13743,6 +14480,11 @@
           <t>Kind: 110003</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -13750,6 +14492,11 @@
           <t>KIND 110003 — Đoán địa điểm (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -13757,6 +14504,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -13860,6 +14612,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -14035,6 +14792,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -14049,6 +14811,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -14092,6 +14859,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -14106,6 +14878,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -14134,6 +14911,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -14162,6 +14944,11 @@
           <t>Ngân hàng địa điểm (Place Bank)</t>
         </is>
       </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -14814,6 +15601,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -14889,6 +15681,11 @@
           <t>Kind: 110004</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -14896,6 +15693,11 @@
           <t>KIND 110004 — Đoán chủ đề (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -14903,6 +15705,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -15006,6 +15813,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -15181,6 +15993,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -15195,6 +16012,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -15238,6 +16060,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -15252,6 +16079,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -15273,6 +16105,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -15301,6 +16138,11 @@
           <t>Ngân hàng danh từ chủ đề (Topic Noun Bank)</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -15924,6 +16766,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
@@ -15981,6 +16828,11 @@
           <t>Kind: 110005</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -15988,6 +16840,11 @@
           <t>KIND 110005 — Nghe hội thoại, chọn hình phù hợp (TOPIK I, Level 1) [ẢNH]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -15995,6 +16852,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -16110,6 +16972,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -16285,6 +17152,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -16328,6 +17200,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -16349,6 +17226,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -16377,6 +17259,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -16391,6 +17278,11 @@
           <t>Quy tắc tạo 4 bức tranh</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -16426,6 +17318,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -16581,6 +17478,11 @@
           <t>Kind: 110006</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -16588,6 +17490,11 @@
           <t>KIND 110006 — Khớp nội dung (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -16595,6 +17502,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -16698,6 +17610,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -16873,6 +17790,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -16887,6 +17809,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -16942,6 +17869,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -17041,6 +17973,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -17062,6 +17999,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -17097,6 +18039,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -17125,6 +18072,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -17226,6 +18178,11 @@
           <t>Kind: 110007</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -17233,6 +18190,11 @@
           <t>KIND 110007 — Ý chính của nữ (TOPIK I, Level 1)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -17240,6 +18202,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -17343,6 +18310,11 @@
           <t>Metadata (từ CSV)</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -17518,6 +18490,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -17532,6 +18509,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -17575,6 +18557,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -17667,6 +18654,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -17695,6 +18687,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -17723,6 +18720,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">

--- a/kinds_Listen_Origin.xlsx
+++ b/kinds_Listen_Origin.xlsx
@@ -3321,7 +3321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3748,49 +3748,77 @@
       <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Không có bẫy text rõ ràng — đáp án là hình ảnh, không phải text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc audio</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>`trap_action_swap`</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Bức sai có đúng bối cảnh nhưng sai hành động</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>• Hội thoại ngắn giữa 남자/여자 (2-3 lượt nói) mô tả một tình huống cụ thể</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>`trap_context_swap`</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Bức sai có đúng hành động nhưng sai bối cảnh</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>• Format: 남자: ...\n여자: ...\n남자: ... hoặc 여자: ...\n남자: ...\n여자: ...</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• Nội dung: hội thoại mô tả tình huống sinh hoạt (giặt đồ, ở tiệm, mua hàng, sửa chữa...)</t>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Bức sai đúng tổng thể nhưng sai chi tiết nhỏ (đối tượng, vị trí tay)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc đáp án</t>
+          <t>Cấu trúc audio</t>
         </is>
       </c>
       <c r="B45" s="10" t="n"/>
@@ -3802,255 +3830,288 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>• q_answer: ["①", "②", "③", "④"]</t>
+          <t>• Hội thoại ngắn giữa 남자/여자 (2-3 lượt nói) mô tả một tình huống cụ thể</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>• q_image: có (tất cả 147 câu đều có ảnh)</t>
+          <t>• Format: 남자: ...\n여자: ...\n남자: ... hoặc 여자: ...\n남자: ...\n여자: ...</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>• 4 bức tranh minh họa các cảnh khác nhau → dùng q_image_description để mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>Cách mô tả ảnh (q_image_description)</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
+          <t>• Nội dung: hội thoại mô tả tình huống sinh hoạt (giặt đồ, ở tiệm, mua hàng, sửa chữa...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>• q_answer: ["①", "②", "③", "④"]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>Mỗi bức tranh mô tả một cảnh sinh hoạt. Mô tả bao gồm: ai đang làm gì, ở đâu, chi tiết quan trọng phân biệt các bức. Tương tự format 110005.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>Phong cách hình ảnh (từ đề thi thật)</t>
+          <t>• q_image: có (tất cả 147 câu đều có ảnh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>• q_text: rỗng</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>• Tranh vẽ tay đen trắng, phong cách manga/manhwa Hàn Quốc (giống 110005)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>• 4 tranh đánh số ①②③④, mỗi tranh = 1 hành động tiếp theo có thể xảy ra</t>
-        </is>
-      </c>
+          <t>• 4 bức tranh minh họa các cảnh khác nhau → dùng q_image_description để mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Cách mô tả ảnh (q_image_description)</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>• Mỗi tranh có 2 nhân vật tương tác, bối cảnh chi tiết hơn TOPIK I</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>• Bối cảnh đa dạng: bưu điện, sông suối, công viên, cửa hàng</t>
+          <t>Mỗi bức tranh mô tả một cảnh sinh hoạt. Mô tả bao gồm: ai đang làm gì, ở đâu, chi tiết quan trọng phân biệt các bức. Tương tự format 110005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Phong cách hình ảnh (từ đề thi thật)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>• Hành động phức tạp hơn 110005: cần suy luận "tiếp theo sẽ làm gì"</t>
+          <t>• Tranh vẽ tay đen trắng, phong cách manga/manhwa Hàn Quốc (giống 110005)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>• Nét vẽ sạch, grayscale, không màu</t>
+          <t>• 4 tranh đánh số ①②③④, mỗi tranh = 1 hành động tiếp theo có thể xảy ra</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>• Kích thước: 4 tranh xếp 2x2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc tạo 4 bức tranh</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
+          <t>• Mỗi tranh có 2 nhân vật tương tác, bối cảnh chi tiết hơn TOPIK I</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>• Bối cảnh đa dạng: bưu điện, sông suối, công viên, cửa hàng</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>• Bức đúng: khớp chính xác nội dung audio (hành động + bối cảnh + đối tượng)</t>
+          <t>• Hành động phức tạp hơn 110005: cần suy luận "tiếp theo sẽ làm gì"</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>• Bức sai 1: đúng bối cảnh nhưng sai hành động</t>
+          <t>• Nét vẽ sạch, grayscale, không màu</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
+          <t>• Kích thước: 4 tranh xếp 2x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc tạo 4 bức tranh</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>• Bức đúng: khớp chính xác nội dung audio (hành động + bối cảnh + đối tượng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>• Bức sai 1: đúng bối cảnh nhưng sai hành động</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
           <t>• Bức sai 2: đúng hành động nhưng sai bối cảnh</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>• Bức sai 3: khác hoàn toàn nhưng dùng 1 yếu tố gây nhầm lẫn từ audio</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B65" s="10" t="n"/>
-      <c r="C65" s="10" t="n"/>
-      <c r="D65" s="10" t="n"/>
-      <c r="E65" s="10" t="n"/>
-      <c r="F65" s="10" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "g_text_audio": "여자: 이거 좀 봐 주실래요? 옷에 커피를 쏟았어요.\n남자: 어디 좀 볼까요? 음..., 세탁하면 깨끗해질 거예요. 언제까지 해 드리면 돼요?\n여자: 내일까지 해 주세요.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [{</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_image_description": {</t>
-        </is>
-      </c>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "1": "여자가 세탁소에서 남자 직원에게 커피 얼룩이 묻은 옷을 보여주고 있다.",</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "2": "여자가 세탁소에서 남자 직원에게 돈을 내고 있다.",</t>
+          <t xml:space="preserve">  "g_text_audio": "여자: 이거 좀 봐 주실래요? 옷에 커피를 쏟았어요.\n남자: 어디 좀 볼까요? 음..., 세탁하면 깨끗해질 거예요. 언제까지 해 드리면 돼요?\n여자: 내일까지 해 주세요.",</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "3": "여자가 카페에서 남자에게 커피를 쏟고 있다.",</t>
+          <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "4": "남자가 여자에게 깨끗한 옷을 전달하고 있다."</t>
+          <t xml:space="preserve">    "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "1": "여자가 세탁소에서 남자 직원에게 커피 얼룩이 묻은 옷을 보여주고 있다.",</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_answer": ["①", "②", "③", "④"],</t>
+          <t xml:space="preserve">      "2": "여자가 세탁소에서 남자 직원에게 돈을 내고 있다.",</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 1</t>
+          <t xml:space="preserve">      "3": "여자가 카페에서 남자에게 커피를 쏟고 있다.",</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">      "4": "남자가 여자에게 깨끗한 옷을 전달하고 있다."</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_answer": ["①", "②", "③", "④"],</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_correct": 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="46">
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A50:F50"/>
@@ -4061,22 +4122,19 @@
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A67:F67"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A77:F77"/>
@@ -4086,10 +4144,12 @@
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A69:F69"/>
@@ -4105,7 +4165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4528,49 +4588,77 @@
       <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Không có bẫy text rõ ràng — đáp án là biểu đồ, không phải text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc audio</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>`trap_number_shift`</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Biểu đồ sai thay đổi số liệu (cao↔thấp, tăng↔giảm)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>• Một người dẫn (남자 hoặc 여자) đọc đoạn monologue: tin tức, báo cáo số liệu, kết quả khảo sát</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>`trap_comparison_flip`</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Đảo chiều so sánh giữa các mục trong biểu đồ</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>• Format: 남자: ... hoặc 여자: ... (single narrator)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• Nội dung: số liệu cụ thể — tỷ lệ, thứ hạng, xu hướng tăng/giảm</t>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Đúng xu hướng chung nhưng sai chi tiết cụ thể</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc đáp án</t>
+          <t>Cấu trúc audio</t>
         </is>
       </c>
       <c r="B45" s="10" t="n"/>
@@ -4582,262 +4670,295 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>• q_answer: ["①", "②", "③", "④"]</t>
+          <t>• Một người dẫn (남자 hoặc 여자) đọc đoạn monologue: tin tức, báo cáo số liệu, kết quả khảo sát</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>• q_image: có (tất cả 53 câu đều có ảnh)</t>
+          <t>• Format: 남자: ... hoặc 여자: ... (single narrator)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>• 4 biểu đồ khác nhau → dùng q_image_description để mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>Cách mô tả ảnh (q_image_description)</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
+          <t>• Nội dung: số liệu cụ thể — tỷ lệ, thứ hạng, xu hướng tăng/giảm</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>• q_answer: ["①", "②", "③", "④"]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>Mỗi biểu đồ mô tả bằng: loại biểu đồ (thanh/tròn/đường), nhãn trục, chú thích (legend), các điểm dữ liệu cụ thể.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>Phong cách hình ảnh (từ đề thi thật)</t>
+          <t>• q_image: có (tất cả 53 câu đều có ảnh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>• q_text: rỗng</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>• 4 cặp biểu đồ đánh số ①②③④, mỗi đáp án = 1 cặp biểu đồ</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>• Mỗi cặp gồm: 원그래프 (biểu đồ tròn) + 막대그래프 (biểu đồ thanh ngang)</t>
-        </is>
-      </c>
+          <t>• 4 biểu đồ khác nhau → dùng q_image_description để mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Cách mô tả ảnh (q_image_description)</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>• Biểu đồ tròn: chia 2 phần (있다/없다 hoặc 예/아니오) với tỷ lệ % khác nhau giữa các đáp án</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>• Biểu đồ thanh: xếp hạng 1위, 2위, 3위 với nhãn text, thứ tự khác nhau giữa các đáp án</t>
+          <t>Mỗi biểu đồ mô tả bằng: loại biểu đồ (thanh/tròn/đường), nhãn trục, chú thích (legend), các điểm dữ liệu cụ thể.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Phong cách hình ảnh (từ đề thi thật)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>• Tiêu đề chung cho tất cả: ví dụ "친환경 농산물 구매 경험", "친환경 농산물 구매 이유"</t>
+          <t>• 4 cặp biểu đồ đánh số ①②③④, mỗi đáp án = 1 cặp biểu đồ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>• Grayscale, nền trắng, viền đen mỏng</t>
+          <t>• Mỗi cặp gồm: 원그래프 (biểu đồ tròn) + 막대그래프 (biểu đồ thanh ngang)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>• Các đáp án khác nhau ở: tỷ lệ % trong biểu đồ tròn VÀ thứ tự xếp hạng trong biểu đồ thanh</t>
+          <t>• Biểu đồ tròn: chia 2 phần (있다/없다 hoặc 예/아니오) với tỷ lệ % khác nhau giữa các đáp án</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>• Kích thước: 4 cặp xếp 2x2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc tạo 4 biểu đồ</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
+          <t>• Biểu đồ thanh: xếp hạng 1위, 2위, 3위 với nhãn text, thứ tự khác nhau giữa các đáp án</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>• Tiêu đề chung cho tất cả: ví dụ "친환경 농산물 구매 경험", "친환경 농산물 구매 이유"</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>• Biểu đồ đúng: khớp chính xác số liệu trong audio (tỷ lệ, thứ tự, xu hướng)</t>
+          <t>• Grayscale, nền trắng, viền đen mỏng</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>• Biểu đồ sai 1: đảo thứ tự các mục (ví dụ: 20대 và 10대 đổi chỗ)</t>
+          <t>• Các đáp án khác nhau ở: tỷ lệ % trong biểu đồ tròn VÀ thứ tự xếp hạng trong biểu đồ thanh</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
+          <t>• Kích thước: 4 cặp xếp 2x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc tạo 4 biểu đồ</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>• Biểu đồ đúng: khớp chính xác số liệu trong audio (tỷ lệ, thứ tự, xu hướng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>• Biểu đồ sai 1: đảo thứ tự các mục (ví dụ: 20대 và 10대 đổi chỗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
           <t>• Biểu đồ sai 2: thay đổi tỷ lệ/giá trị (ví dụ: tăng thành giảm)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>• Biểu đồ sai 3: sai loại biểu đồ hoặc sai nhãn (ví dụ: biểu đồ tròn thay vì thanh, nhãn bị đổi)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="9" t="inlineStr">
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-      <c r="E66" s="10" t="n"/>
-      <c r="F66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "g_text_audio": "남자: 스마트폰 사용자가 많아지면서 모바일 쇼핑 이용객이 급격히 증가한 것으로 나타났습니다. 20대가 가장 많이 이용하는 것으로 나타났으며 10대가 그 뒤를 이었습니다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [{</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_image_description": {</t>
-        </is>
-      </c>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "1": "막대 그래프. X축: 연령대(10대, 20대, 30대, 40대). Y축: 이용자 수. 20대가 가장 높고, 10대가 두 번째.",</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "2": "막대 그래프. X축: 연령대(10대, 20대, 30대, 40대). Y축: 이용자 수. 10대가 가장 높고, 20대가 두 번째.",</t>
+          <t xml:space="preserve">  "g_text_audio": "남자: 스마트폰 사용자가 많아지면서 모바일 쇼핑 이용객이 급격히 증가한 것으로 나타났습니다. 20대가 가장 많이 이용하는 것으로 나타났으며 10대가 그 뒤를 이었습니다.",</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "3": "원형 그래프. 20대 40%, 10대 30%, 30대 20%, 40대 10%.",</t>
+          <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "4": "꺾은선 그래프. 모바일 쇼핑 이용객이 감소하는 추세. 20대가 가장 낮음."</t>
+          <t xml:space="preserve">    "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "1": "막대 그래프. X축: 연령대(10대, 20대, 30대, 40대). Y축: 이용자 수. 20대가 가장 높고, 10대가 두 번째.",</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_answer": ["①", "②", "③", "④"],</t>
+          <t xml:space="preserve">      "2": "막대 그래프. X축: 연령대(10대, 20대, 30대, 40대). Y축: 이용자 수. 10대가 가장 높고, 20대가 두 번째.",</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 1</t>
+          <t xml:space="preserve">      "3": "원형 그래프. 20대 40%, 10대 30%, 30대 20%, 40대 10%.",</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">      "4": "꺾은선 그래프. 모바일 쇼핑 이용객이 감소하는 추세. 20대가 가장 낮음."</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_answer": ["①", "②", "③", "④"],</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_correct": 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="47">
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A50:F50"/>
@@ -4848,22 +4969,20 @@
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A67:F67"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A77:F77"/>
@@ -4873,6 +4992,7 @@
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
@@ -7756,7 +7876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F313"/>
+  <dimension ref="A1:F316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8883,1256 +9003,1241 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
+          <t>110001, 110002, 110003, 110004, 110006, 110007, 210002-210007</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>`trap_similar_word`</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Similar Word</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án chứa từ phát âm/dạng tương tự (e.g. 약국↔학교, 운동↔운전)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>110003, 110004</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>`trap_partial_topic`</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Partial Topic</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án chỉ đề cập một phần nội dung, không phải chủ đề chính</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>110004</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="13" t="inlineStr">
+        <is>
+          <t>Nhóm 2: Bẫy phủ định (Negation Traps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>`trap_neg_없안`</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Negation 없/안/아니</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án sai thêm 없다/안/아니다 để đảo nghĩa</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
           <t>110001, 110002, 110006, 110007, 210002-210007</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm 2: Bẫy phủ định (Negation Traps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="14" t="inlineStr">
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="13" t="inlineStr">
+        <is>
+          <t>Nhóm 3: Bẫy cấu trúc (Structural Traps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B126" s="14" t="inlineStr">
+      <c r="B132" s="14" t="inlineStr">
         <is>
           <t>Nhãn tiếng Anh</t>
         </is>
       </c>
-      <c r="C126" s="14" t="inlineStr">
+      <c r="C132" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="D126" s="14" t="inlineStr">
+      <c r="D132" s="14" t="inlineStr">
         <is>
           <t>Kind áp dụng</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>`trap_neg_없안`</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>Negation 없/안/아니</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án sai thêm 없다/안/아니다 để đảo nghĩa</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>`trap_same_ending`</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Same-Ending Pattern</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Cả 4 đáp án kết thúc cùng dạng ngữ pháp</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
         <is>
           <t>110001, 110002, 110006, 110007, 210002-210007</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm 3: Bẫy cấu trúc (Structural Traps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="14" t="inlineStr">
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="13" t="inlineStr">
+        <is>
+          <t>Nhóm 4: Bẫy nội dung (Content Traps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B130" s="14" t="inlineStr">
+      <c r="B136" s="14" t="inlineStr">
         <is>
           <t>Nhãn tiếng Anh</t>
         </is>
       </c>
-      <c r="C130" s="14" t="inlineStr">
+      <c r="C136" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="D130" s="14" t="inlineStr">
+      <c r="D136" s="14" t="inlineStr">
         <is>
           <t>Kind áp dụng</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>`trap_same_ending`</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>Same-Ending Pattern</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>Cả 4 đáp án kết thúc cùng dạng ngữ pháp</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>110001, 110002, 110006, 110007, 210002-210007</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm 4: Bẫy nội dung (Content Traps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B134" s="14" t="inlineStr">
-        <is>
-          <t>Nhãn tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C134" s="14" t="inlineStr">
-        <is>
-          <t>Mô tả</t>
-        </is>
-      </c>
-      <c r="D134" s="14" t="inlineStr">
-        <is>
-          <t>Kind áp dụng</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>`trap_subject_swap`</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>Subject Swap</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>Gán hành động/ý kiến cho sai người (남↔여)</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>110006, 110008_1, 110008_2, 110008_3, 210003-210007</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>`trap_opinion_swap`</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>Opinion Swap</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án sai thể hiện ý kiến người nói kia</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>110007, 210005</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>`trap_detail_distort`</t>
+          <t>`trap_subject_swap`</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Detail Distortion</t>
+          <t>Subject Swap</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Bóp méo chi tiết nhỏ</t>
+          <t>Gán hành động/ý kiến cho sai người (남↔여)</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>110005, 110008_1, 110008_2, 110008_3</t>
+          <t>110006, 110008_1, 110008_2, 110008_3, 210003-210007</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>`trap_partial_truth`</t>
+          <t>`trap_opinion_swap`</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Partial Truth</t>
+          <t>Opinion Swap</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Đáp án sai chứa &gt;30% từ đúng</t>
+          <t>Đáp án sai thể hiện ý kiến người nói kia</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>110006, 110008_1, 110008_2</t>
+          <t>110007, 210005</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>`trap_wrong_inference`</t>
+          <t>`trap_detail_distort`</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Wrong Inference</t>
+          <t>Detail Distortion</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Suy luận hợp lý nhưng không được nêu</t>
+          <t>Bóp méo chi tiết nhỏ</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>110008_1, 110008_2, 110008_3</t>
+          <t>110005, 110008_1, 110008_2, 110008_3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>`trap_cause_effect_swap`</t>
+          <t>`trap_partial_truth`</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Cause-Effect Swap</t>
+          <t>Partial Truth</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Đảo quan hệ nhân quả</t>
+          <t>Đáp án sai chứa &gt;30% từ đúng</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>110006, 110008_3</t>
+          <t>110006, 110008_1, 110008_2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>`trap_scope_change`</t>
+          <t>`trap_wrong_inference`</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Scope Change</t>
+          <t>Wrong Inference</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Thay đổi từ chỉ phạm vi: 모든↔일부</t>
+          <t>Suy luận hợp lý nhưng không được nêu</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>110006, 110007, 110008_3</t>
+          <t>110008_1, 110008_2, 110008_3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>`trap_temporal_distort`</t>
+          <t>`trap_cause_effect_swap`</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Temporal Distortion</t>
+          <t>Cause-Effect Swap</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>Đảo biểu thức thời gian</t>
+          <t>Đảo quan hệ nhân quả</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>110006, 110008_2</t>
+          <t>110006, 110008_3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>`trap_comparison_flip`</t>
+          <t>`trap_scope_change`</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Comparison Flip</t>
+          <t>Scope Change</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Đảo chiều so sánh</t>
+          <t>Thay đổi từ chỉ phạm vi: 모든↔일부</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>110006</t>
+          <t>110006, 110007, 110008_3</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>`trap_action_swap`</t>
+          <t>`trap_temporal_distort`</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Action Swap</t>
+          <t>Temporal Distortion</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>Đáp án sai thay đổi hành động</t>
+          <t>Đảo biểu thức thời gian</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>110005</t>
+          <t>110006, 110008_2</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
+          <t>`trap_comparison_flip`</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Comparison Flip</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>Đảo chiều so sánh</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>110006, 210001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>`trap_action_swap`</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Action Swap</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án sai thay đổi hành động</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>110005, 210001_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
           <t>`trap_context_swap`</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>Context Swap</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>Đáp án sai thay đổi bối cảnh</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>110005</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="13" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>110005, 210001_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>`trap_number_shift`</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>Number/Time Shift</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Thay đổi số liệu biểu đồ</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>210001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="13" t="inlineStr">
         <is>
           <t>Quy tắc gán nhãn bẫy</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="11" t="inlineStr">
-        <is>
-          <t>• Mỗi câu hỏi có thể có NHIỀU nhãn bẫy cùng lúc (ví dụ: trap_shared_noun + trap_neg_없안 + trap_same_ending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>• Gán nhãn dựa trên ĐÁP ÁN SAI, không phải đáp án đúng</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>• Chỉ gán khi có bằng chứng rõ ràng, không suy đoán</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>Đặc điểm câu hỏi (question_feature)</t>
-        </is>
-      </c>
-      <c r="B152" s="10" t="n"/>
-      <c r="C152" s="10" t="n"/>
-      <c r="D152" s="10" t="n"/>
-      <c r="E152" s="10" t="n"/>
-      <c r="F152" s="10" t="n"/>
+          <t>• Mỗi câu hỏi có thể có NHIỀU nhãn bẫy cùng lúc (ví dụ: trap_shared_noun + trap_neg_없안 + trap_same_ending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>• Gán nhãn dựa trên ĐÁP ÁN SAI, không phải đáp án đúng</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
+          <t>• Chỉ gán khi có bằng chứng rõ ràng, không suy đoán</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>Đặc điểm câu hỏi (question_feature)</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="n"/>
+      <c r="C155" s="10" t="n"/>
+      <c r="D155" s="10" t="n"/>
+      <c r="E155" s="10" t="n"/>
+      <c r="F155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
           <t>Nhãn gán cho q_text — xác định kiểu thông tin cần trích xuất.</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="13" t="inlineStr">
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="13" t="inlineStr">
         <is>
           <t>Nhóm câu hỏi có q_text</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="14" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B155" s="14" t="inlineStr">
+      <c r="B158" s="14" t="inlineStr">
         <is>
           <t>Nhãn tiếng Anh</t>
         </is>
       </c>
-      <c r="C155" s="14" t="inlineStr">
+      <c r="C158" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="D155" s="14" t="inlineStr">
+      <c r="D158" s="14" t="inlineStr">
         <is>
           <t>Số lượng</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>`qf_content_match`</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>Content Match</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>"들은 내용으로 맞는 것을 고르십시오"</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>`qf_what`</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>What (General)</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>"무엇입니까?", "무엇을 삽니까?"</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>`qf_what_doing`</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>What Doing</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>"무엇을 하고 있습니까?"</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>228</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>`qf_where`</t>
+          <t>`qf_content_match`</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Where/Which</t>
+          <t>Content Match</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>"어디입니까?", "어느 나라?"</t>
+          <t>"들은 내용으로 맞는 것을 고르십시오"</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>733</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>`qf_central_thought`</t>
+          <t>`qf_what`</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Central Thought</t>
+          <t>What (General)</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>"중심 생각으로 맞는 것"</t>
+          <t>"무엇입니까?", "무엇을 삽니까?"</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>409</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>`qf_attitude`</t>
+          <t>`qf_what_doing`</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Attitude/Manner</t>
+          <t>What Doing</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>"태도로 맞는 것을 고르십시오"</t>
+          <t>"무엇을 하고 있습니까?"</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>228</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>`qf_why`</t>
+          <t>`qf_where`</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Why/Reason</t>
+          <t>Where/Which</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>"왜?", "이유"</t>
+          <t>"어디입니까?", "어느 나라?"</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>223</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>`qf_when_time`</t>
+          <t>`qf_central_thought`</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>When/Time</t>
+          <t>Central Thought</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>"언제?", "몇 시?", "얼마 동안?"</t>
+          <t>"중심 생각으로 맞는 것"</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>120</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>`qf_who`</t>
+          <t>`qf_attitude`</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Who</t>
+          <t>Attitude/Manner</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>"누구입니까?"</t>
+          <t>"태도로 맞는 것을 고르십시오"</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>126</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>`qf_how_many`</t>
+          <t>`qf_why`</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>How Many</t>
+          <t>Why/Reason</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>"몇 명?", "몇 개?"</t>
+          <t>"왜?", "이유"</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>122</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>`qf_intention`</t>
+          <t>`qf_when_time`</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Intention</t>
+          <t>When/Time</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>"말하는 의도를 고르십시오"</t>
+          <t>"언제?", "몇 시?", "얼마 동안?"</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>117</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>`qf_how_much`</t>
+          <t>`qf_who`</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>How Much (Price)</t>
+          <t>Who</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>"얼마입니까?"</t>
+          <t>"누구입니까?"</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
+          <t>`qf_how_many`</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>How Many</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>"몇 명?", "몇 개?"</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>`qf_intention`</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>Intention</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>"말하는 의도를 고르십시오"</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>`qf_how_much`</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>How Much (Price)</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>"얼마입니까?"</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
           <t>`qf_how`</t>
         </is>
       </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>How/Method</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
+      <c r="C171" s="6" t="inlineStr">
         <is>
           <t>"어떻게?", "방법"</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="22" customHeight="1">
-      <c r="A170" s="13" t="inlineStr">
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="13" t="inlineStr">
         <is>
           <t>Nhóm câu hỏi KHÔNG có q_text</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="11" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="11" t="inlineStr">
         <is>
           <t>Kiểu câu hỏi xác định từ kind + title, không cần q_text:</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="14" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B172" s="14" t="inlineStr">
+      <c r="B175" s="14" t="inlineStr">
         <is>
           <t>Kind áp dụng</t>
         </is>
       </c>
-      <c r="C172" s="14" t="inlineStr">
+      <c r="C175" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>`qf_direct_qa`</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>110001</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>Nghe câu hỏi → chọn câu trả lời trực tiếp</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="6" t="inlineStr">
-        <is>
-          <t>`qf_next_utterance`</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>110002, 210002</t>
-        </is>
-      </c>
-      <c r="C174" s="6" t="inlineStr">
-        <is>
-          <t>Nghe hội thoại → chọn câu nối tiếp</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>`qf_guess_place`</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>110003</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>Nghe → đoán địa điểm</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>`qf_guess_topic`</t>
+          <t>`qf_direct_qa`</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>110004</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>Nghe → đoán chủ đề đang nói</t>
+          <t>Nghe câu hỏi → chọn câu trả lời trực tiếp</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>`qf_match_image`</t>
+          <t>`qf_next_utterance`</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>110005, 210001_1</t>
+          <t>110002, 210002</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Nghe → chọn hình khớp</t>
+          <t>Nghe hội thoại → chọn câu nối tiếp</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>`qf_match_graph`</t>
+          <t>`qf_guess_place`</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>210001_2</t>
+          <t>110003</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>Nghe số liệu → chọn biểu đồ</t>
+          <t>Nghe → đoán địa điểm</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>`qf_match_content`</t>
+          <t>`qf_guess_topic`</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>110006, 210004</t>
+          <t>110004</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Nghe → chọn phát biểu khớp nội dung</t>
+          <t>Nghe → đoán chủ đề đang nói</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>`qf_predict_action`</t>
+          <t>`qf_match_image`</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>210003</t>
+          <t>110005, 210001_1</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>Nghe → dự đoán hành động tiếp theo</t>
+          <t>Nghe → chọn hình khớp</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>`qf_main_opinion`</t>
+          <t>`qf_match_graph`</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>110007, 210005</t>
+          <t>210001_2</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Nghe → xác định ý kiến chính (남/여)</t>
+          <t>Nghe số liệu → chọn biểu đồ</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
+          <t>`qf_match_content`</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>110006, 210004</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>Nghe → chọn phát biểu khớp nội dung</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>`qf_predict_action`</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>210003</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>Nghe → dự đoán hành động tiếp theo</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>`qf_main_opinion`</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>110007, 210005</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>Nghe → xác định ý kiến chính (남/여)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
           <t>`qf_multi_comprehension`</t>
         </is>
       </c>
-      <c r="B182" s="6" t="inlineStr">
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>110008_1, 110008_2, 110008_3, 210006</t>
         </is>
       </c>
-      <c r="C182" s="6" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
         <is>
           <t>Nghe dài và trả lời 2 câu hỏi</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="11" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="9" t="inlineStr">
+    <row r="188" ht="22" customHeight="1">
+      <c r="A188" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc ngữ pháp trong audio (grammar_semantic)</t>
         </is>
       </c>
-      <c r="B185" s="10" t="n"/>
-      <c r="C185" s="10" t="n"/>
-      <c r="D185" s="10" t="n"/>
-      <c r="E185" s="10" t="n"/>
-      <c r="F185" s="10" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="11" t="inlineStr">
-        <is>
-          <t>Phân tích ngữ pháp theo Ý NGHĨA — phát hiện thực tế từ audio 5.701 câu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="13" t="inlineStr">
-        <is>
-          <t>Phân bố theo level (chỉ liệt kê ≥5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="11" t="inlineStr">
-        <is>
-          <t>Level 1 (1.692 câu):</t>
-        </is>
-      </c>
+      <c r="B188" s="10" t="n"/>
+      <c r="C188" s="10" t="n"/>
+      <c r="D188" s="10" t="n"/>
+      <c r="E188" s="10" t="n"/>
+      <c r="F188" s="10" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>gram_honorific_시(35%), gram_request_세요(34%), gram_cond_면(16%), gram_contrast_는데(14%), gram_cause_니까(12%), gram_honorific_습니다(12%), gram_cause_어서(11%), gram_intent_겠(11%), gram_request_주세요(11%), gram_intent_려고(7%), gram_purpose_러(6%), gram_contrast_지만(6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="11" t="inlineStr">
-        <is>
-          <t>Level 2 (1.767 câu):</t>
+          <t>Phân tích ngữ pháp theo Ý NGHĨA — phát hiện thực tế từ audio 5.701 câu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="13" t="inlineStr">
+        <is>
+          <t>Phân bố theo level (chỉ liệt kê ≥5%)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
+          <t>Level 1 (1.692 câu):</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>gram_honorific_시(35%), gram_request_세요(34%), gram_cond_면(16%), gram_contrast_는데(14%), gram_cause_니까(12%), gram_honorific_습니다(12%), gram_cause_어서(11%), gram_intent_겠(11%), gram_request_주세요(11%), gram_intent_려고(7%), gram_purpose_러(6%), gram_contrast_지만(6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>Level 2 (1.767 câu):</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
           <t>gram_cond_면(50%), gram_honorific_습니다(47%), gram_contrast_는데(45%), gram_cause_니까(26%), gram_prog_고있(24%), gram_intent_겠(22%), gram_contrast_지만(22%), gram_honorific_시(21%), gram_request_세요(17%), gram_cause_어서(17%), gram_time_면서(14%), gram_cause_때문(14%), gram_compare_보다(10%), gram_result_게되(10%)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="13" t="inlineStr">
+    <row r="195" ht="22" customHeight="1">
+      <c r="A195" s="13" t="inlineStr">
         <is>
           <t>Bảng nhãn ngữ pháp theo ý nghĩa</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="14" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B193" s="14" t="inlineStr">
+      <c r="B196" s="14" t="inlineStr">
         <is>
           <t>Cấu trúc</t>
         </is>
       </c>
-      <c r="C193" s="14" t="inlineStr">
+      <c r="C196" s="14" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
-      <c r="D193" s="14" t="inlineStr">
+      <c r="D196" s="14" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="E193" s="14" t="inlineStr">
+      <c r="E196" s="14" t="inlineStr">
         <is>
           <t>L2</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>`gram_cause_어서`</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
-        <is>
-          <t>~어서/아서</t>
-        </is>
-      </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>Nguyên nhân (nhẹ)</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>`gram_cause_니까`</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
-        <is>
-          <t>~니까</t>
-        </is>
-      </c>
-      <c r="C195" s="6" t="inlineStr">
-        <is>
-          <t>Nguyên nhân (nhấn mạnh)</t>
-        </is>
-      </c>
-      <c r="D195" s="6" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="E195" s="6" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="6" t="inlineStr">
-        <is>
-          <t>`gram_cause_때문`</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
-        <is>
-          <t>~때문에</t>
-        </is>
-      </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>Nguyên nhân (danh từ hóa)</t>
-        </is>
-      </c>
-      <c r="D196" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E196" s="6" t="inlineStr">
-        <is>
-          <t>14%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>`gram_cond_면`</t>
+          <t>`gram_cause_어서`</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>~(으)면</t>
+          <t>~어서/아서</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>Điều kiện</t>
+          <t>Nguyên nhân (nhẹ)</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>17%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>`gram_contrast_지만`</t>
+          <t>`gram_cause_니까`</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>~지만</t>
+          <t>~니까</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>Đối lập trực tiếp</t>
+          <t>Nguyên nhân (nhấn mạnh)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>26%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>`gram_contrast_는데`</t>
+          <t>`gram_cause_때문`</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>~는데/은데</t>
+          <t>~때문에</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>Bối cảnh/đối lập mềm</t>
+          <t>Nguyên nhân (danh từ hóa)</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
           <t>14%</t>
-        </is>
-      </c>
-      <c r="E199" s="6" t="inlineStr">
-        <is>
-          <t>45%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>`gram_intent_려고`</t>
+          <t>`gram_cond_면`</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>~(으)려고</t>
+          <t>~(으)면</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>Ý định</t>
+          <t>Điều kiện</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>`gram_intent_겠`</t>
+          <t>`gram_contrast_지만`</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>~겠어요/겠습니다</t>
+          <t>~지만</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>Dự định/suy đoán</t>
+          <t>Đối lập trực tiếp</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -10144,71 +10249,71 @@
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>`gram_ability_수있`</t>
+          <t>`gram_contrast_는데`</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>~(을) 수 있다</t>
+          <t>~는데/은데</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>Khả năng (có thể)</t>
+          <t>Bối cảnh/đối lập mềm</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>`gram_request_세요`</t>
+          <t>`gram_intent_려고`</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>~(으)세요</t>
+          <t>~(으)려고</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>Yêu cầu lịch sự</t>
+          <t>Ý định</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>`gram_request_주세요`</t>
+          <t>`gram_intent_겠`</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>~주세요</t>
+          <t>~겠어요/겠습니다</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>Nhờ vả cụ thể</t>
+          <t>Dự định/suy đoán</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
@@ -10218,24 +10323,24 @@
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>`gram_compare_보다`</t>
+          <t>`gram_ability_수있`</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>~보다</t>
+          <t>~(을) 수 있다</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>So sánh</t>
+          <t>Khả năng (có thể)</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -10245,78 +10350,78 @@
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>`gram_compare_제일`</t>
+          <t>`gram_request_세요`</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>제일/가장</t>
+          <t>~(으)세요</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>So sánh nhất</t>
+          <t>Yêu cầu lịch sự</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>17%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>`gram_prog_고있`</t>
+          <t>`gram_request_주세요`</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>~고 있다</t>
+          <t>~주세요</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>Đang diễn ra</t>
+          <t>Nhờ vả cụ thể</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="E207" s="6" t="inlineStr">
-        <is>
-          <t>24%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>`gram_result_게되`</t>
+          <t>`gram_compare_보다`</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>~게 되다</t>
+          <t>~보다</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>Kết quả thay đổi</t>
+          <t>So sánh</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -10333,17 +10438,17 @@
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>`gram_time_면서`</t>
+          <t>`gram_compare_제일`</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>~면서</t>
+          <t>제일/가장</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>Đồng thời</t>
+          <t>So sánh nhất</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
@@ -10353,24 +10458,24 @@
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>8%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>`gram_time_동안`</t>
+          <t>`gram_prog_고있`</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>~동안</t>
+          <t>~고 있다</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>Khoảng thời gian</t>
+          <t>Đang diễn ra</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
@@ -10380,78 +10485,78 @@
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>`gram_honorific_시`</t>
+          <t>`gram_result_게되`</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>~시/셨/세요</t>
+          <t>~게 되다</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>Kính ngữ (시)</t>
+          <t>Kết quả thay đổi</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>`gram_honorific_습니다`</t>
+          <t>`gram_time_면서`</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>~습니다/ㅂ니다</t>
+          <t>~면서</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>Kính ngữ trang trọng</t>
+          <t>Đồng thời</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>14%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>`gram_purpose_기위해`</t>
+          <t>`gram_time_동안`</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>~기 위해(서)</t>
+          <t>~동안</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>Mục đích (formal)</t>
+          <t>Khoảng thời gian</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
@@ -10461,1066 +10566,1130 @@
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>7%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
+          <t>`gram_honorific_시`</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>~시/셨/세요</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>Kính ngữ (시)</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>`gram_honorific_습니다`</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>~습니다/ㅂ니다</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>Kính ngữ trang trọng</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>`gram_purpose_기위해`</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>~기 위해(서)</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>Mục đích (formal)</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
           <t>`gram_purpose_러`</t>
         </is>
       </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>~(으)러</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
         <is>
           <t>Mục đích (đi đâu)</t>
         </is>
       </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E217" s="6" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="11" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="11" t="inlineStr">
         <is>
           <t>*Ghi chú: "—" = dưới 5%, vẫn tồn tại nhưng không đủ phổ biến để làm nhãn chính.*</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="22" customHeight="1">
-      <c r="A217" s="13" t="inlineStr">
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="13" t="inlineStr">
         <is>
           <t>Ngữ pháp trong đáp án (answer_grammar)</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="14" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B218" s="14" t="inlineStr">
+      <c r="B221" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="C218" s="14" t="inlineStr">
+      <c r="C221" s="14" t="inlineStr">
         <is>
           <t>Kind áp dụng</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>`ans_informal_polite`</t>
-        </is>
-      </c>
-      <c r="B219" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án dùng ~어요/아요</t>
-        </is>
-      </c>
-      <c r="C219" s="6" t="inlineStr">
-        <is>
-          <t>110001, 110002</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="6" t="inlineStr">
-        <is>
-          <t>`ans_noun_phrase`</t>
-        </is>
-      </c>
-      <c r="B220" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án là danh từ/cụm danh từ</t>
-        </is>
-      </c>
-      <c r="C220" s="6" t="inlineStr">
-        <is>
-          <t>110003, 110004, 110008_2 (Q1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>`ans_image`</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án là hình ảnh (không có text)</t>
-        </is>
-      </c>
-      <c r="C221" s="6" t="inlineStr">
-        <is>
-          <t>110005, 210001_1, 210001_2</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>`ans_formal_polite`</t>
+          <t>`ans_informal_polite`</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>Đáp án dùng ~ㅂ니다/습니다</t>
+          <t>Đáp án dùng ~어요/아요</t>
         </is>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>110006, 110007, 210002, 110008_1 (Q2), 110008_2 (Q2), 110008_3 (Q2)</t>
+          <t>110001, 110002</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>`ans_plain_form`</t>
+          <t>`ans_noun_phrase`</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>Đáp án dùng thể trần thuật (~ㄴ다/한다/이다)</t>
+          <t>Đáp án là danh từ/cụm danh từ</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>210003, 210004, 210005, 210006, 210007</t>
+          <t>110003, 110004, 110008_2 (Q1)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>`ans_purpose_phrase`</t>
+          <t>`ans_image`</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>Đáp án dùng ~기 위해 (mục đích)</t>
+          <t>Đáp án là hình ảnh (không có text)</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>110008_1 (Q1)</t>
+          <t>110005, 210001_1, 210001_2</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
+          <t>`ans_formal_polite`</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án dùng ~ㅂ니다/습니다</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>110006, 110007, 210002, 110008_1 (Q2), 110008_2 (Q2), 110008_3 (Q2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>`ans_plain_form`</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án dùng thể trần thuật (~ㄴ다/한다/이다)</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>210003, 210004, 210005, 210006, 210007</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>`ans_purpose_phrase`</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án dùng ~기 위해 (mục đích)</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>110008_1 (Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
           <t>`ans_reason_phrase`</t>
         </is>
       </c>
-      <c r="B225" s="6" t="inlineStr">
+      <c r="B228" s="6" t="inlineStr">
         <is>
           <t>Đáp án dùng ~아/어서 (lý do)</t>
         </is>
       </c>
-      <c r="C225" s="6" t="inlineStr">
+      <c r="C228" s="6" t="inlineStr">
         <is>
           <t>110008_3 (Q1)</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="11" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="22" customHeight="1">
-      <c r="A228" s="9" t="inlineStr">
+    <row r="231" ht="22" customHeight="1">
+      <c r="A231" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio (audio_format)</t>
         </is>
       </c>
-      <c r="B228" s="10" t="n"/>
-      <c r="C228" s="10" t="n"/>
-      <c r="D228" s="10" t="n"/>
-      <c r="E228" s="10" t="n"/>
-      <c r="F228" s="10" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="14" t="inlineStr">
+      <c r="B231" s="10" t="n"/>
+      <c r="C231" s="10" t="n"/>
+      <c r="D231" s="10" t="n"/>
+      <c r="E231" s="10" t="n"/>
+      <c r="F231" s="10" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B229" s="14" t="inlineStr">
+      <c r="B232" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="C229" s="14" t="inlineStr">
+      <c r="C232" s="14" t="inlineStr">
         <is>
           <t>Số lượng</t>
         </is>
       </c>
-      <c r="D229" s="14" t="inlineStr">
+      <c r="D232" s="14" t="inlineStr">
         <is>
           <t>Kind chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="6" t="inlineStr">
-        <is>
-          <t>`audio_dialog_short`</t>
-        </is>
-      </c>
-      <c r="B230" s="6" t="inlineStr">
-        <is>
-          <t>Hội thoại 남/여 ngắn (1-2 lượt)</t>
-        </is>
-      </c>
-      <c r="C230" s="6" t="inlineStr">
-        <is>
-          <t>~720</t>
-        </is>
-      </c>
-      <c r="D230" s="6" t="inlineStr">
-        <is>
-          <t>110003-110005, 210001_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="6" t="inlineStr">
-        <is>
-          <t>`audio_dialog_medium`</t>
-        </is>
-      </c>
-      <c r="B231" s="6" t="inlineStr">
-        <is>
-          <t>Hội thoại 남/여 trung bình (3-4 lượt)</t>
-        </is>
-      </c>
-      <c r="C231" s="6" t="inlineStr">
-        <is>
-          <t>1.547</t>
-        </is>
-      </c>
-      <c r="D231" s="6" t="inlineStr">
-        <is>
-          <t>110006-110007, 210002-210005</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="6" t="inlineStr">
-        <is>
-          <t>`audio_dialog_long`</t>
-        </is>
-      </c>
-      <c r="B232" s="6" t="inlineStr">
-        <is>
-          <t>Hội thoại 남/여 dài (5+ lượt)</t>
-        </is>
-      </c>
-      <c r="C232" s="6" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="D232" s="6" t="inlineStr">
-        <is>
-          <t>210006, 210007</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>`audio_single_sentence`</t>
+          <t>`audio_dialog_short`</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>Câu đơn (15-50 ký tự)</t>
+          <t>Hội thoại 남/여 ngắn (1-2 lượt)</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>~830</t>
+          <t>~720</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>110001, 110002</t>
+          <t>110003-110005, 210001_1</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
+          <t>`audio_dialog_medium`</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>Hội thoại 남/여 trung bình (3-4 lượt)</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>1.547</t>
+        </is>
+      </c>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>110006-110007, 210002-210005</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>`audio_dialog_long`</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>Hội thoại 남/여 dài (5+ lượt)</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t>210006, 210007</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>`audio_single_sentence`</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>Câu đơn (15-50 ký tự)</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>~830</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr">
+        <is>
+          <t>110001, 110002</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
           <t>`audio_monologue`</t>
         </is>
       </c>
-      <c r="B234" s="6" t="inlineStr">
+      <c r="B237" s="6" t="inlineStr">
         <is>
           <t>Độc thoại/tin tức/bài giảng</t>
         </is>
       </c>
-      <c r="C234" s="6" t="inlineStr">
+      <c r="C237" s="6" t="inlineStr">
         <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D234" s="6" t="inlineStr">
+      <c r="D237" s="6" t="inlineStr">
         <is>
           <t>210001_2, 210007</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="11" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="237" ht="22" customHeight="1">
-      <c r="A237" s="9" t="inlineStr">
+    <row r="240" ht="22" customHeight="1">
+      <c r="A240" s="9" t="inlineStr">
         <is>
           <t>Thang độ khó (Difficulty Scale)</t>
         </is>
       </c>
-      <c r="B237" s="10" t="n"/>
-      <c r="C237" s="10" t="n"/>
-      <c r="D237" s="10" t="n"/>
-      <c r="E237" s="10" t="n"/>
-      <c r="F237" s="10" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="14" t="inlineStr">
+      <c r="B240" s="10" t="n"/>
+      <c r="C240" s="10" t="n"/>
+      <c r="D240" s="10" t="n"/>
+      <c r="E240" s="10" t="n"/>
+      <c r="F240" s="10" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="14" t="inlineStr">
         <is>
           <t>Mức</t>
         </is>
       </c>
-      <c r="B238" s="14" t="inlineStr">
+      <c r="B241" s="14" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C238" s="14" t="inlineStr">
+      <c r="C241" s="14" t="inlineStr">
         <is>
           <t>Kiểu suy luận</t>
         </is>
       </c>
-      <c r="D238" s="14" t="inlineStr">
+      <c r="D241" s="14" t="inlineStr">
         <is>
           <t>Nhãn</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
-        <is>
-          <t>110001</t>
-        </is>
-      </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>`direct_match`</t>
-        </is>
-      </c>
-      <c r="D239" s="6" t="inlineStr">
-        <is>
-          <t>Hỏi-đáp đơn giản</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
-        <is>
-          <t>110002</t>
-        </is>
-      </c>
-      <c r="C240" s="6" t="inlineStr">
-        <is>
-          <t>`pragmatic_response`</t>
-        </is>
-      </c>
-      <c r="D240" s="6" t="inlineStr">
-        <is>
-          <t>Chọn câu nối tiếp</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
-        <is>
-          <t>110003, 110004</t>
-        </is>
-      </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>`keyword_inference`</t>
-        </is>
-      </c>
-      <c r="D241" s="6" t="inlineStr">
-        <is>
-          <t>Đoán địa điểm/chủ đề</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>110005</t>
+          <t>110001</t>
         </is>
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>`scene_matching`</t>
+          <t>`direct_match`</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>Chọn hình</t>
+          <t>Hỏi-đáp đơn giản</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>110006, 210002, 210001_1</t>
+          <t>110002</t>
         </is>
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>`content_matching` / `scene_matching`</t>
+          <t>`pragmatic_response`</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>Khớp nội dung</t>
+          <t>Chọn câu nối tiếp</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>210003, 210004, 210001_2</t>
+          <t>110003, 110004</t>
         </is>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>`action_prediction` / `graph_matching`</t>
+          <t>`keyword_inference`</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>Hành động / biểu đồ</t>
+          <t>Đoán địa điểm/chủ đề</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>110007, 210005, 110008_1, 110008_2, 110008_3, 210006</t>
+          <t>110005</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>`opinion_extraction` / `multi_comprehension`</t>
+          <t>`scene_matching`</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>Ý chính / 2 câu hỏi</t>
+          <t>Chọn hình</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>110006, 210002, 210001_1</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>`content_matching` / `scene_matching`</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="inlineStr">
+        <is>
+          <t>Khớp nội dung</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B247" s="6" t="inlineStr">
+        <is>
+          <t>210003, 210004, 210001_2</t>
+        </is>
+      </c>
+      <c r="C247" s="6" t="inlineStr">
+        <is>
+          <t>`action_prediction` / `graph_matching`</t>
+        </is>
+      </c>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t>Hành động / biểu đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B248" s="6" t="inlineStr">
+        <is>
+          <t>110007, 210005, 110008_1, 110008_2, 110008_3, 210006</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>`opinion_extraction` / `multi_comprehension`</t>
+        </is>
+      </c>
+      <c r="D248" s="6" t="inlineStr">
+        <is>
+          <t>Ý chính / 2 câu hỏi</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B246" s="6" t="inlineStr">
+      <c r="B249" s="6" t="inlineStr">
         <is>
           <t>210007</t>
         </is>
       </c>
-      <c r="C246" s="6" t="inlineStr">
+      <c r="C249" s="6" t="inlineStr">
         <is>
           <t>`academic_comprehension`</t>
         </is>
       </c>
-      <c r="D246" s="6" t="inlineStr">
+      <c r="D249" s="6" t="inlineStr">
         <is>
           <t>Chương trình giáo dục</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="22" customHeight="1">
-      <c r="A248" s="13" t="inlineStr">
+    <row r="251" ht="22" customHeight="1">
+      <c r="A251" s="13" t="inlineStr">
         <is>
           <t>Mô tả kiểu suy luận (reasoning_type)</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="14" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B249" s="14" t="inlineStr">
+      <c r="B252" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="6" t="inlineStr">
-        <is>
-          <t>`direct_match`</t>
-        </is>
-      </c>
-      <c r="B250" s="6" t="inlineStr">
-        <is>
-          <t>Ghép câu hỏi với câu trả lời trực tiếp</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="6" t="inlineStr">
-        <is>
-          <t>`pragmatic_response`</t>
-        </is>
-      </c>
-      <c r="B251" s="6" t="inlineStr">
-        <is>
-          <t>Chọn phản hồi phù hợp ngữ cảnh giao tiếp</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="6" t="inlineStr">
-        <is>
-          <t>`keyword_inference`</t>
-        </is>
-      </c>
-      <c r="B252" s="6" t="inlineStr">
-        <is>
-          <t>Suy luận địa điểm/chủ đề từ từ khóa</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>`scene_matching`</t>
+          <t>`direct_match`</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>Nghe audio, chọn bức tranh minh họa khớp</t>
+          <t>Ghép câu hỏi với câu trả lời trực tiếp</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>`detail_extraction`</t>
+          <t>`pragmatic_response`</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>Trích xuất chi tiết cụ thể từ hội thoại</t>
+          <t>Chọn phản hồi phù hợp ngữ cảnh giao tiếp</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>`content_matching`</t>
+          <t>`keyword_inference`</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>So khớp phát biểu với nội dung hội thoại</t>
+          <t>Suy luận địa điểm/chủ đề từ từ khóa</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>`graph_matching`</t>
+          <t>`scene_matching`</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>Nghe số liệu, chọn biểu đồ khớp</t>
+          <t>Nghe audio, chọn bức tranh minh họa khớp</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>`action_prediction`</t>
+          <t>`detail_extraction`</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>Dự đoán hành động tiếp theo</t>
+          <t>Trích xuất chi tiết cụ thể từ hội thoại</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>`opinion_extraction`</t>
+          <t>`content_matching`</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>Xác định ý kiến/quan điểm chính</t>
+          <t>So khớp phát biểu với nội dung hội thoại</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>`multi_comprehension`</t>
+          <t>`graph_matching`</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>Trả lời 2 câu hỏi từ 1 đoạn</t>
+          <t>Nghe số liệu, chọn biểu đồ khớp</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
+          <t>`action_prediction`</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t>Dự đoán hành động tiếp theo</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>`opinion_extraction`</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>Xác định ý kiến/quan điểm chính</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>`multi_comprehension`</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t>Trả lời 2 câu hỏi từ 1 đoạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
           <t>`academic_comprehension`</t>
         </is>
       </c>
-      <c r="B260" s="6" t="inlineStr">
+      <c r="B263" s="6" t="inlineStr">
         <is>
           <t>Hiểu nội dung phỏng vấn/tọa đàm chuyên sâu</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="11" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="263" ht="22" customHeight="1">
-      <c r="A263" s="9" t="inlineStr">
+    <row r="266" ht="22" customHeight="1">
+      <c r="A266" s="9" t="inlineStr">
         <is>
           <t>Cấp độ giao tiếp trong audio (speech_level)</t>
         </is>
       </c>
-      <c r="B263" s="10" t="n"/>
-      <c r="C263" s="10" t="n"/>
-      <c r="D263" s="10" t="n"/>
-      <c r="E263" s="10" t="n"/>
-      <c r="F263" s="10" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="11" t="inlineStr">
+      <c r="B266" s="10" t="n"/>
+      <c r="C266" s="10" t="n"/>
+      <c r="D266" s="10" t="n"/>
+      <c r="E266" s="10" t="n"/>
+      <c r="F266" s="10" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="11" t="inlineStr">
         <is>
           <t>Xác định mức trang trọng khi tạo audio. Chi tiết ngữ pháp cụ thể → xem phần [grammar_semantic](#cấu-trúc-ngữ-pháp-trong-audio-grammar_semantic).</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="14" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="14" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B265" s="14" t="inlineStr">
+      <c r="B268" s="14" t="inlineStr">
         <is>
           <t>Audio chính</t>
         </is>
       </c>
-      <c r="C265" s="14" t="inlineStr">
+      <c r="C268" s="14" t="inlineStr">
         <is>
           <t>Đáp án</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="6" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>`informal_polite` (~어요/세요) 46%, `connective` (~니까/는데) 19%</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
         <is>
           <t>`informal_polite`</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="6" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>`modifier` (~ㄴ/는) 31%, `connective` 27%, `formal_polite` (~ㅂ니다) 16%</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
         <is>
           <t>`plain_form` (~ㄴ다/한다) — xem answer_grammar</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="11" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="11" t="inlineStr">
         <is>
           <t>Quy tắc: Audio Level 1 dùng informal_polite. Audio Level 2 pha trộn. Đáp án Level 2 thường dùng plain_form.</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="22" customHeight="1">
-      <c r="A271" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc chung khi gen câu hỏi</t>
-        </is>
-      </c>
-      <c r="B271" s="10" t="n"/>
-      <c r="C271" s="10" t="n"/>
-      <c r="D271" s="10" t="n"/>
-      <c r="E271" s="10" t="n"/>
-      <c r="F271" s="10" t="n"/>
-    </row>
-    <row r="272" ht="22" customHeight="1">
-      <c r="A272" s="13" t="inlineStr">
-        <is>
-          <t>1. Chất lượng nội dung tiếng Hàn</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>• Dùng ngữ pháp đúng level (xem bảng speech_level + grammar_semantic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="11" t="inlineStr">
-        <is>
-          <t>• Hội thoại tự nhiên, đa dạng chủ đề đời sống</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="11" t="inlineStr">
-        <is>
-          <t>• KHÔNG lặp lại từ vựng/ngữ cảnh giữa các câu trong cùng batch</t>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="22" customHeight="1">
+      <c r="A274" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc chung khi gen câu hỏi</t>
+        </is>
+      </c>
+      <c r="B274" s="10" t="n"/>
+      <c r="C274" s="10" t="n"/>
+      <c r="D274" s="10" t="n"/>
+      <c r="E274" s="10" t="n"/>
+      <c r="F274" s="10" t="n"/>
+    </row>
+    <row r="275" ht="22" customHeight="1">
+      <c r="A275" s="13" t="inlineStr">
+        <is>
+          <t>1. Chất lượng nội dung tiếng Hàn</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>• Level 2: pha trộn 2-3 topic categories mỗi câu</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="22" customHeight="1">
-      <c r="A277" s="13" t="inlineStr">
-        <is>
-          <t>2. Xây dựng đáp án sai (distractor)</t>
+          <t>• Dùng ngữ pháp đúng level (xem bảng speech_level + grammar_semantic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="11" t="inlineStr">
+        <is>
+          <t>• Hội thoại tự nhiên, đa dạng chủ đề đời sống</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>• Tuân theo tỷ lệ bẫy của từng kind (xem file kind tương ứng)</t>
+          <t>• KHÔNG lặp lại từ vựng/ngữ cảnh giữa các câu trong cùng batch</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>• Phải hợp lý nhưng SAI về nội dung</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="11" t="inlineStr">
-        <is>
-          <t>• Tái sử dụng từ vựng audio khi kind yêu cầu shared_word</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="22" customHeight="1">
-      <c r="A281" s="13" t="inlineStr">
-        <is>
-          <t>3. Giải thích (explain)</t>
+          <t>• Level 2: pha trộn 2-3 topic categories mỗi câu</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="22" customHeight="1">
+      <c r="A280" s="13" t="inlineStr">
+        <is>
+          <t>2. Xây dựng đáp án sai (distractor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="11" t="inlineStr">
+        <is>
+          <t>• Tuân theo tỷ lệ bẫy của từng kind (xem file kind tương ứng)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>• vi: Dịch cả 4 đáp án → dấu -------------------- → giải thích đáp án đúng</t>
+          <t>• Phải hợp lý nhưng SAI về nội dung</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>• en: Tương tự bằng tiếng Anh</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="11" t="inlineStr">
-        <is>
-          <t>• Highlight từ vựng/ngữ pháp quan trọng</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="22" customHeight="1">
-      <c r="A285" s="13" t="inlineStr">
-        <is>
-          <t>4. Số lượng</t>
+          <t>• Tái sử dụng từ vựng audio khi kind yêu cầu shared_word</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="22" customHeight="1">
+      <c r="A284" s="13" t="inlineStr">
+        <is>
+          <t>3. Giải thích (explain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="11" t="inlineStr">
+        <is>
+          <t>• vi: Dịch cả 4 đáp án → dấu -------------------- → giải thích đáp án đúng</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>• Mặc định: 5 câu mỗi kind nếu user không chỉ định</t>
+          <t>• en: Tương tự bằng tiếng Anh</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>• Tối đa: 20 câu mỗi lần</t>
+          <t>• Highlight từ vựng/ngữ pháp quan trọng</t>
         </is>
       </c>
     </row>
     <row r="288" ht="22" customHeight="1">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>5. Kiểm tra sau khi gen (Validation Checklist)</t>
+          <t>4. Số lượng</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>• [ ] q_correct nằm trong 1-4</t>
+          <t>• Mặc định: 5 câu mỗi kind nếu user không chỉ định</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>• [ ] 4 đáp án không trùng nhau</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="11" t="inlineStr">
-        <is>
-          <t>• [ ] Audio là tiếng Hàn tự nhiên</t>
+          <t>• Tối đa: 20 câu mỗi lần</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="22" customHeight="1">
+      <c r="A291" s="13" t="inlineStr">
+        <is>
+          <t>5. Kiểm tra sau khi gen (Validation Checklist)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Ngữ pháp đúng level</t>
+          <t>• [ ] q_correct nằm trong 1-4</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bẫy đúng phân bố của kind</t>
+          <t>• [ ] 4 đáp án không trùng nhau</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bản dịch (vi/en) chính xác</t>
+          <t>• [ ] Audio là tiếng Hàn tự nhiên</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>• [ ] explain chứa dịch 4 đáp án + lý do đáp án đúng</t>
+          <t>• [ ] Ngữ pháp đúng level</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>• [ ] count_question khớp số phần tử trong content</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="22" customHeight="1">
-      <c r="A297" s="9" t="inlineStr">
-        <is>
-          <t>Workflow</t>
-        </is>
-      </c>
-      <c r="B297" s="10" t="n"/>
-      <c r="C297" s="10" t="n"/>
-      <c r="D297" s="10" t="n"/>
-      <c r="E297" s="10" t="n"/>
-      <c r="F297" s="10" t="n"/>
+          <t>• [ ] Bẫy đúng phân bố của kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] Bản dịch (vi/en) chính xác</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>1. User chỉ định kind → đọc file kinds/{kind}.md</t>
+          <t>• [ ] explain chứa dịch 4 đáp án + lý do đáp án đúng</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>2. Hỏi số lượng (mặc định 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="11" t="inlineStr">
-        <is>
-          <t>3. Gen câu hỏi theo JSON format + quy tắc kind + chiến lược bẫy</t>
-        </is>
-      </c>
+          <t>• [ ] count_question khớp số phần tử trong content</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="22" customHeight="1">
+      <c r="A300" s="9" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B300" s="10" t="n"/>
+      <c r="C300" s="10" t="n"/>
+      <c r="D300" s="10" t="n"/>
+      <c r="E300" s="10" t="n"/>
+      <c r="F300" s="10" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>4. Lưu JSON tạm → chạy scripts/save_listen.py để tách CSV theo kind</t>
+          <t>1. User chỉ định kind → đọc file kinds/{kind}.md</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
+          <t>2. Hỏi số lượng (mặc định 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="11" t="inlineStr">
+        <is>
+          <t>3. Gen câu hỏi theo JSON format + quy tắc kind + chiến lược bẫy</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="11" t="inlineStr">
+        <is>
+          <t>4. Lưu JSON tạm → chạy scripts/save_listen.py để tách CSV theo kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="11" t="inlineStr">
+        <is>
           <t>5. Validate theo checklist</t>
         </is>
       </c>
     </row>
-    <row r="303" ht="22" customHeight="1">
-      <c r="A303" s="13" t="inlineStr">
+    <row r="306" ht="22" customHeight="1">
+      <c r="A306" s="13" t="inlineStr">
         <is>
           <t>Lưu kết quả bằng script</t>
         </is>
       </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="12" t="inlineStr">
-        <is>
-          <t># Lưu CSV theo kind + JSON + merge tổng</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="12" t="inlineStr">
-        <is>
-          <t>python skills/topik-listen-gen-origin/scripts/save_listen.py gen_temp.json -o output/listen-origin --json --merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="12" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="12" t="inlineStr">
         <is>
-          <t># Chỉ validate</t>
+          <t># Lưu CSV theo kind + JSON + merge tổng</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="12" t="inlineStr">
         <is>
-          <t>python skills/topik-listen-gen-origin/scripts/save_listen.py gen_temp.json --validate-only</t>
+          <t>python skills/topik-listen-gen-origin/scripts/save_listen.py gen_temp.json -o output/listen-origin --json --merge</t>
         </is>
       </c>
     </row>
@@ -11530,19 +11699,36 @@
     <row r="310">
       <c r="A310" s="12" t="inlineStr">
         <is>
-          <t># Append thêm batch mới</t>
+          <t># Chỉ validate</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="12" t="inlineStr">
         <is>
+          <t>python skills/topik-listen-gen-origin/scripts/save_listen.py gen_temp.json --validate-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="12" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="12" t="inlineStr">
+        <is>
+          <t># Append thêm batch mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="12" t="inlineStr">
+        <is>
           <t>python skills/topik-listen-gen-origin/scripts/save_listen.py new_batch.json --append</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" s="11" t="inlineStr">
+    <row r="316">
+      <c r="A316" s="11" t="inlineStr">
         <is>
           <t>Output: output/listen-origin/level_{1,2}/{kind}.csv</t>
         </is>
@@ -11550,23 +11736,23 @@
     </row>
   </sheetData>
   <mergeCells count="175">
+    <mergeCell ref="A174:F174"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A118:F118"/>
     <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A133:F133"/>
     <mergeCell ref="A189:F189"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A239:F239"/>
     <mergeCell ref="A301:F301"/>
     <mergeCell ref="A95:F95"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A150:F150"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A263:F263"/>
     <mergeCell ref="A303:F303"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A290:F290"/>
@@ -11576,8 +11762,9 @@
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A152:F152"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A121:F121"/>
     <mergeCell ref="A280:F280"/>
-    <mergeCell ref="A121:F121"/>
     <mergeCell ref="A274:F274"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A288:F288"/>
@@ -11588,14 +11775,12 @@
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A186:F186"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A266:F266"/>
     <mergeCell ref="A291:F291"/>
     <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A228:F228"/>
-    <mergeCell ref="A237:F237"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
@@ -11605,34 +11790,35 @@
     <mergeCell ref="A292:F292"/>
     <mergeCell ref="A286:F286"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A236:F236"/>
-    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A267:F267"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A285:F285"/>
     <mergeCell ref="A294:F294"/>
     <mergeCell ref="A306:F306"/>
+    <mergeCell ref="A195:F195"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="A278:F278"/>
     <mergeCell ref="A151:F151"/>
-    <mergeCell ref="A278:F278"/>
     <mergeCell ref="A188:F188"/>
     <mergeCell ref="A311:F311"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A262:F262"/>
     <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A240:F240"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A230:F230"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A127:F127"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A314:F314"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A304:F304"/>
-    <mergeCell ref="A216:F216"/>
     <mergeCell ref="A98:F98"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A296:F296"/>
@@ -11640,11 +11826,9 @@
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A88:F88"/>
     <mergeCell ref="A153:F153"/>
-    <mergeCell ref="A227:F227"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A217:F217"/>
     <mergeCell ref="A282:F282"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A56:F56"/>
@@ -11652,16 +11836,17 @@
     <mergeCell ref="A154:F154"/>
     <mergeCell ref="A272:F272"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A129:F129"/>
     <mergeCell ref="A313:F313"/>
+    <mergeCell ref="A251:F251"/>
     <mergeCell ref="A307:F307"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A116:F116"/>
     <mergeCell ref="A309:F309"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A131:F131"/>
     <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A231:F231"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A299:F299"/>
     <mergeCell ref="A10:F10"/>
@@ -11670,11 +11855,12 @@
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A173:F173"/>
     <mergeCell ref="A295:F295"/>
     <mergeCell ref="A83:F83"/>
     <mergeCell ref="A276:F276"/>
     <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A270:F270"/>
+    <mergeCell ref="A157:F157"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A310:F310"/>
     <mergeCell ref="A279:F279"/>
@@ -11687,10 +11873,10 @@
     <mergeCell ref="A287:F287"/>
     <mergeCell ref="A281:F281"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A271:F271"/>
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A264:F264"/>
+    <mergeCell ref="A316:F316"/>
+    <mergeCell ref="A193:F193"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A273:F273"/>
@@ -11699,25 +11885,25 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A192:F192"/>
-    <mergeCell ref="A248:F248"/>
     <mergeCell ref="A297:F297"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A302:F302"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A185:F185"/>
     <mergeCell ref="A298:F298"/>
+    <mergeCell ref="A219:F219"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A312:F312"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A96:F96"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A184:F184"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A170:F170"/>
+    <mergeCell ref="A156:F156"/>
     <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A220:F220"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A148:F148"/>
     <mergeCell ref="A275:F275"/>
     <mergeCell ref="A284:F284"/>
     <mergeCell ref="A6:F6"/>
@@ -11736,7 +11922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -12121,725 +12307,735 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>audio_format</t>
+          <t>question_feature</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>`audio_dialog_long`</t>
+          <t>`qf_multi_comprehension`</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>audio_format</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>`audio_dialog_long`</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
           <t>answer_grammar</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>`ans_plain_form`</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Bẫy</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>`trap_shared_noun`</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Dùng lại từ vựng từ audio. **Bẫy chính**</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>`trap_same_ending`</t>
+          <t>`trap_shared_noun`</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Các đáp án kết thúc giống nhau</t>
+          <t>Dùng lại từ vựng từ audio. **Bẫy chính**</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>`trap_neg_없안`</t>
+          <t>`trap_same_ending`</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Đảo nghĩa bằng phủ định</t>
+          <t>Các đáp án kết thúc giống nhau</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
+          <t>`trap_neg_없안`</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Đảo nghĩa bằng phủ định</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
           <t>`trap_subject_swap`</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Gán ý kiến/hành động cho sai người (hiếm)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>⚠️ Bẫy chính: trap_shared_noun (75%) + trap_same_ending (48%) — đáp án sai dùng từ trong audio kết hợp cùng dạng kết thúc để gây nhầm lẫn.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>• Hội thoại dài giữa 남자/여자 (4-6 lượt nói), thảo luận chuyên sâu về một vấn đề</t>
-        </is>
-      </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>• Format: 여자: ...\n남자: ...\n여자: ...\n남자: ...\n여자: ...\n남자: ...</t>
+          <t>• Hội thoại dài giữa 남자/여자 (4-6 lượt nói), thảo luận chuyên sâu về một vấn đề</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
+          <t>• Format: 여자: ...\n남자: ...\n여자: ...\n남자: ...\n여자: ...\n남자: ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
           <t>• Nội dung: hội thoại dài, có trao đổi quan điểm, chứa nhiều chi tiết và lập luận</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>• Mỗi audio có 2 câu hỏi phụ, mỗi câu hỏi có 4 đáp án dạng văn bản</t>
-        </is>
-      </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
+          <t>• Mỗi audio có 2 câu hỏi phụ, mỗi câu hỏi có 4 đáp án dạng văn bản</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
           <t>• q_text: LUÔN CÓ cho cả 2 câu hỏi phụ</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Dạng q_text câu hỏi phụ 1 (thường gặp)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>Dạng q_text</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>Số lần</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>`남자는 무엇을 하고 있는지 고르십시오.`</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>83</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>`남자는 누구인지 고르십시오.`</t>
+          <t>`남자는 무엇을 하고 있는지 고르십시오.`</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>`무엇에 대한 내용인지 맞는 것을 고르십시오.`</t>
+          <t>`남자는 누구인지 고르십시오.`</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
+          <t>`무엇에 대한 내용인지 맞는 것을 고르십시오.`</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
           <t>`여자가 남자에게 말하는 의도를 고르십시오.`</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>Dạng q_text câu hỏi phụ 2 (thường gặp)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>Dạng q_text</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>Số lần</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>`들은 내용으로 맞는 것을 고르십시오.`</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>267</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>`남자의 중심 생각으로 맞는 것을 고르십시오.`</t>
+          <t>`들은 내용으로 맞는 것을 고르십시오.`</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>267</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>`남자의 생각으로 맞는 것을 고르십시오.`</t>
+          <t>`남자의 중심 생각으로 맞는 것을 고르십시오.`</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
+          <t>`남자의 생각으로 맞는 것을 고르십시오.`</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
           <t>`남자의 태도로 맞는 것을 고르십시오.`</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>1. Audio PHẢI là hội thoại dài (4-6 lượt nói) giữa 남자/여자</t>
-        </is>
-      </c>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>2. PHẢI tạo đúng 2 câu hỏi phụ, mỗi câu có q_text riêng và 4 đáp án</t>
+          <t>1. Audio PHẢI là hội thoại dài (4-6 lượt nói) giữa 남자/여자</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>3. Đáp án sai PHẢI dùng lại từ vựng từ audio (trap_shared_noun 75%)</t>
+          <t>2. PHẢI tạo đúng 2 câu hỏi phụ, mỗi câu có q_text riêng và 4 đáp án</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>4. Ít nhất 2 đáp án sai của mỗi câu hỏi PHẢI kết thúc cùng dạng (trap_same_ending)</t>
+          <t>3. Đáp án sai PHẢI dùng lại từ vựng từ audio (trap_shared_noun 75%)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>5. Câu hỏi phụ 1 thường hỏi về nhân vật, hành động, chủ đề, hoặc ý đồ</t>
+          <t>4. Ít nhất 2 đáp án sai của mỗi câu hỏi PHẢI kết thúc cùng dạng (trap_same_ending)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
+          <t>5. Câu hỏi phụ 1 thường hỏi về nhân vật, hành động, chủ đề, hoặc ý đồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
           <t>6. Câu hỏi phụ 2 thường hỏi về nội dung chi tiết, ý chính, hoặc thái độ</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="10" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>Audio:</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t>여자: 기숙사 신청 날짜를 착각해서 신청을 못했는데 어쩌지?</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>남자: 학교에서 소개해 주는 집이 있는데 신청해 볼래? 다른 학생들하고 보증금을 나눠 내고 집을 같이 빌리는 방식이라서...</t>
+          <t>여자: 기숙사 신청 날짜를 착각해서 신청을 못했는데 어쩌지?</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>여자: 그럼 집을 같이 쓰는 거네? 한집에서 공동생활 하는 건 좀 불편할 것 같은데...</t>
+          <t>남자: 학교에서 소개해 주는 집이 있는데 신청해 볼래? 다른 학생들하고 보증금을 나눠 내고 집을 같이 빌리는 방식이라서...</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
+          <t>여자: 그럼 집을 같이 쓰는 거네? 한집에서 공동생활 하는 건 좀 불편할 것 같은데...</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
           <t>남자: 공동생활도 생각보다 괜찮아. 방은 혼자 쓰니까 개인 공간도 있고...</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>Câu hỏi phụ 1 — q_text: 남자의 중심 생각으로 맞는 것을 고르십시오.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>Đáp án:</t>
+          <t>Câu hỏi phụ 1 — q_text: 남자의 중심 생각으로 맞는 것을 고르십시오.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>① 학교에서 소개하는 집은 믿을 만한 집이다. (trap_shared_noun — "학교에서 소개" nhưng không phải ý chính)</t>
+          <t>Đáp án:</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>② 다른 사람과 함께 사는 것은 긍정적인 면도 있다. ✅ (đúng — 남자 cho rằng 공동생활 괜찮아)</t>
+          <t>① 학교에서 소개하는 집은 믿을 만한 집이다. (trap_shared_noun — "학교에서 소개" nhưng không phải ý chính)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>③ 기숙사에 사는 것이 공동생활보다 편하다. (trap_shared_noun — "기숙사", "공동생활" nhưng đảo ý)</t>
+          <t>② 다른 사람과 함께 사는 것은 긍정적인 면도 있다. ✅ (đúng — 남자 cho rằng 공동생활 괜찮아)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>④ 보증금을 나눠 내면 집을 구하기 어렵다. (trap_shared_noun + trap_neg_없안 — "보증금을 나눠 내고" nhưng đảo kết quả)</t>
+          <t>③ 기숙사에 사는 것이 공동생활보다 편하다. (trap_shared_noun — "기숙사", "공동생활" nhưng đảo ý)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>Đúng: ②</t>
+          <t>④ 보증금을 나눠 내면 집을 구하기 어렵다. (trap_shared_noun + trap_neg_없안 — "보증금을 나눠 내고" nhưng đảo kết quả)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>Câu hỏi phụ 2 — q_text: 들은 내용으로 맞는 것을 고르십시오.</t>
+          <t>Đúng: ②</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>Đáp án:</t>
+          <t>Câu hỏi phụ 2 — q_text: 들은 내용으로 맞는 것을 고르십시오.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>① 여자는 기숙사 신청 기간을 놓쳤다. ✅ (đúng — "신청 날짜를 착각해서 신청을 못했는데")</t>
+          <t>Đáp án:</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>② 남자는 기숙사에서 생활하고 있다. (trap_shared_noun — "기숙사" nhưng sai thông tin)</t>
+          <t>① 여자는 기숙사 신청 기간을 놓쳤다. ✅ (đúng — "신청 날짜를 착각해서 신청을 못했는데")</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>③ 학교에서 소개하는 집은 혼자 사용한다. (trap_shared_noun + trap_neg_없안 — "같이 빌리는 방식" nhưng đảo thành "혼자")</t>
+          <t>② 남자는 기숙사에서 생활하고 있다. (trap_shared_noun — "기숙사" nhưng sai thông tin)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>④ 여자는 공동생활을 해 본 적이 있다. (trap_shared_noun — "공동생활" nhưng sai sự thật)</t>
+          <t>③ 학교에서 소개하는 집은 혼자 사용한다. (trap_shared_noun + trap_neg_없안 — "같이 빌리는 방식" nhưng đảo thành "혼자")</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
+          <t>④ 여자는 공동생활을 해 본 적이 있다. (trap_shared_noun — "공동생활" nhưng sai sự thật)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
           <t>Đúng: ①</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="13" t="inlineStr">
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="13" t="inlineStr">
         <is>
           <t>JSON mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "kind": 210006,</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "title": "[21 ~ 22] 다음을 듣고 물음에 답하십시오. (각 2점)",</t>
+          <t xml:space="preserve">  "kind": 210006,</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "audio": "여자: 기숙사 신청 날짜를 착각해서 신청을 못했는데 어쩌지?\n남자: 학교에서 소개해 주는 집이 있는데 신청해 볼래? 다른 학생들하고 보증금을 나눠 내고 집을 같이 빌리는 방식이라서...\n여자: 그럼 집을 같이 쓰는 거네? 한집에서 공동생활 하는 건 좀 불편할 것 같은데...\n남자: 공동생활도 생각보다 괜찮아. 방은 혼자 쓰니까 개인 공간도 있고...",</t>
+          <t xml:space="preserve">  "title": "[21 ~ 22] 다음을 듣고 물음에 답하십시오. (각 2점)",</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "contents": [</t>
+          <t xml:space="preserve">  "audio": "여자: 기숙사 신청 날짜를 착각해서 신청을 못했는데 어쩌지?\n남자: 학교에서 소개해 주는 집이 있는데 신청해 볼래? 다른 학생들하고 보증금을 나눠 내고 집을 같이 빌리는 방식이라서...\n여자: 그럼 집을 같이 쓰는 거네? 한집에서 공동생활 하는 건 좀 불편할 것 같은데...\n남자: 공동생활도 생각보다 괜찮아. 방은 혼자 쓰니까 개인 공간도 있고...",</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {</t>
+          <t xml:space="preserve">  "contents": [</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "남자의 중심 생각으로 맞는 것을 고르십시오.",</t>
+          <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "answers": [</t>
+          <t xml:space="preserve">      "q_text": "남자의 중심 생각으로 맞는 것을 고르십시오.",</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "학교에서 소개하는 집은 믿을 만한 집이다.",</t>
+          <t xml:space="preserve">      "answers": [</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "다른 사람과 함께 사는 것은 긍정적인 면도 있다.",</t>
+          <t xml:space="preserve">        "학교에서 소개하는 집은 믿을 만한 집이다.",</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "기숙사에 사는 것이 공동생활보다 편하다.",</t>
+          <t xml:space="preserve">        "다른 사람과 함께 사는 것은 긍정적인 면도 있다.",</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "보증금을 나눠 내면 집을 구하기 어렵다."</t>
+          <t xml:space="preserve">        "기숙사에 사는 것이 공동생활보다 편하다.",</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ],</t>
+          <t xml:space="preserve">        "보증금을 나눠 내면 집을 구하기 어렵다."</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "correct": 2</t>
+          <t xml:space="preserve">      ],</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "correct": 2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {</t>
+          <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "들은 내용으로 맞는 것을 고르십시오.",</t>
+          <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "answers": [</t>
+          <t xml:space="preserve">      "q_text": "들은 내용으로 맞는 것을 고르십시오.",</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "여자는 기숙사 신청 기간을 놓쳤다.",</t>
+          <t xml:space="preserve">      "answers": [</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "남자는 기숙사에서 생활하고 있다.",</t>
+          <t xml:space="preserve">        "여자는 기숙사 신청 기간을 놓쳤다.",</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "학교에서 소개하는 집은 혼자 사용한다.",</t>
+          <t xml:space="preserve">        "남자는 기숙사에서 생활하고 있다.",</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "여자는 공동생활을 해 본 적이 있다."</t>
+          <t xml:space="preserve">        "학교에서 소개하는 집은 혼자 사용한다.",</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ],</t>
+          <t xml:space="preserve">        "여자는 공동생활을 해 본 적이 있다."</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "correct": 1</t>
+          <t xml:space="preserve">      ],</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    }</t>
+          <t xml:space="preserve">      "correct": 1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ]</t>
+          <t xml:space="preserve">    }</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A90:F90"/>
     <mergeCell ref="A108:F108"/>
     <mergeCell ref="A80:F80"/>
@@ -12857,13 +13053,16 @@
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A86:F86"/>
     <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A71:F71"/>
     <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A71:F71"/>
     <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A126:F126"/>
     <mergeCell ref="A106:F106"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A35:F35"/>
@@ -12877,7 +13076,6 @@
     <mergeCell ref="A122:F122"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A63:F63"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A121:F121"/>
     <mergeCell ref="A115:F115"/>
@@ -12888,10 +13086,11 @@
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="A111:F111"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A92:F92"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A114:F114"/>
+    <mergeCell ref="A64:F64"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A49:F49"/>
@@ -12903,9 +13102,8 @@
     <mergeCell ref="A123:F123"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A103:F103"/>
     <mergeCell ref="A79:F79"/>
-    <mergeCell ref="A103:F103"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A88:F88"/>
@@ -12923,7 +13121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13324,692 +13522,705 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>audio_format</t>
+          <t>question_feature</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>`audio_monologue`</t>
+          <t>`qf_multi_comprehension`</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
+          <t>audio_format</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>`audio_monologue`</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
           <t>answer_grammar</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>`ans_plain_form`</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Bẫy</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>`trap_shared_noun`</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>**GẦN NHƯ LUÔN**. Đáp án sai dùng lại thuật ngữ từ audio</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>`trap_same_ending`</t>
+          <t>`trap_shared_noun`</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Các đáp án kết thúc giống nhau</t>
+          <t>**GẦN NHƯ LUÔN**. Đáp án sai dùng lại thuật ngữ từ audio</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>`trap_neg_않못`</t>
+          <t>`trap_same_ending`</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Đảo nghĩa — phủ định nội dung đã nghe</t>
+          <t>Các đáp án kết thúc giống nhau</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
+          <t>`trap_neg_않못`</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Đảo nghĩa — phủ định nội dung đã nghe</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
           <t>`trap_subject_swap`</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Gán ý kiến cho sai người (rất hiếm)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>⚠️ Bẫy chính: trap_shared_noun rất cao (88%) — đáp án sai tái sử dụng thuật ngữ học thuật từ audio để tạo cảm giác đúng.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>• Dạng phỏng vấn/tọa đàm: 여자 hỏi + 남자 trả lời chuyên sâu, rất dài</t>
-        </is>
-      </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>• Format: 여자: ...\n남자: ...\n여자: ...\n남자: ...</t>
+          <t>• Dạng phỏng vấn/tọa đàm: 여자 hỏi + 남자 trả lời chuyên sâu, rất dài</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>• Nội dung: 여자 đóng vai MC/phóng viên đặt câu hỏi, 남자 là chuyên gia giải thích chuyên sâu</t>
+          <t>• Format: 여자: ...\n남자: ...\n여자: ...\n남자: ...</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
+          <t>• Nội dung: 여자 đóng vai MC/phóng viên đặt câu hỏi, 남자 là chuyên gia giải thích chuyên sâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
           <t>• Ngôn ngữ: trang trọng, nhiều thuật ngữ học thuật, câu dài và phức tạp</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>• Mỗi audio có 2 câu hỏi phụ, mỗi câu hỏi có 4 đáp án dạng văn bản</t>
-        </is>
-      </c>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>• q_text: LUÔN CÓ cho cả 2 câu hỏi phụ</t>
+          <t>• Mỗi audio có 2 câu hỏi phụ, mỗi câu hỏi có 4 đáp án dạng văn bản</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
+          <t>• q_text: LUÔN CÓ cho cả 2 câu hỏi phụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
           <t>• Đáp án dùng ngôn ngữ trang trọng, học thuật</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="13" t="inlineStr">
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>Dạng q_text thường gặp</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>Dạng q_text</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>Số lần</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>`들은 내용과 같은 것을 고르십시오.`</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>`들은 내용과 일치하는 것을 고르십시오.`</t>
+          <t>`들은 내용과 같은 것을 고르십시오.`</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>`남자의 태도로 가장 알맞은 것을 고르십시오.`</t>
+          <t>`들은 내용과 일치하는 것을 고르십시오.`</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>`여자의 태도로 가장 알맞은 것을 고르십시오.`</t>
+          <t>`남자의 태도로 가장 알맞은 것을 고르십시오.`</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>`이 담화 앞의 내용으로 알맞은 것을 고르십시오.`</t>
+          <t>`여자의 태도로 가장 알맞은 것을 고르십시오.`</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
+          <t>`이 담화 앞의 내용으로 알맞은 것을 고르십시오.`</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
           <t>`여자가 말하는 방식으로 가장 알맞은 것을 고르십시오.`</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="10" t="n"/>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>1. Audio PHẢI là dạng phỏng vấn/tọa đàm: 여자 hỏi, 남자 trả lời chuyên sâu</t>
-        </is>
-      </c>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>2. PHẢI tạo đúng 2 câu hỏi phụ, mỗi câu có q_text riêng và 4 đáp án</t>
+          <t>1. Audio PHẢI là dạng phỏng vấn/tọa đàm: 여자 hỏi, 남자 trả lời chuyên sâu</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>3. Đáp án sai PHẢI dùng lại thuật ngữ từ audio (trap_shared_noun 88%)</t>
+          <t>2. PHẢI tạo đúng 2 câu hỏi phụ, mỗi câu có q_text riêng và 4 đáp án</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>4. Ít nhất 1 đáp án sai PHẢI đảo nghĩa nội dung đã nghe (trap_neg_않못 13%)</t>
+          <t>3. Đáp án sai PHẢI dùng lại thuật ngữ từ audio (trap_shared_noun 88%)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>5. Ngôn ngữ audio và đáp án PHẢI trang trọng, học thuật</t>
+          <t>4. Ít nhất 1 đáp án sai PHẢI đảo nghĩa nội dung đã nghe (trap_neg_않못 13%)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
+          <t>5. Ngôn ngữ audio và đáp án PHẢI trang trọng, học thuật</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
           <t>6. 남자 PHẢI giải thích dài, chuyên sâu như một chuyên gia</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>Audio:</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>여자: 박사님이 저술하신 '1만 시간의 법칙'이 요즘 화제를 모으고 있는데요, 아직 읽어 보지 않은 분들을 위해 소개 좀 해 주시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>남자: '1만 시간의 법칙'은 어떤 분야든 만 시간을 투자해야 전문성이 쌓이고 성공할 수 있는 기본 조건이 갖춰진다는 법칙입니다. 하지만 단순히 시간만 채우는 것이 아니라 자신의 한계를 넘어서려는 의식적인 노력이 필요합니다.</t>
+          <t>여자: 박사님이 저술하신 '1만 시간의 법칙'이 요즘 화제를 모으고 있는데요, 아직 읽어 보지 않은 분들을 위해 소개 좀 해 주시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>여자: 그렇다면 시간 투자만으로는 부족하다는 말씀이신가요?</t>
+          <t>남자: '1만 시간의 법칙'은 어떤 분야든 만 시간을 투자해야 전문성이 쌓이고 성공할 수 있는 기본 조건이 갖춰진다는 법칙입니다. 하지만 단순히 시간만 채우는 것이 아니라 자신의 한계를 넘어서려는 의식적인 노력이 필요합니다.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
+          <t>여자: 그렇다면 시간 투자만으로는 부족하다는 말씀이신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
           <t>남자: 네, 맞습니다. 같은 시간을 투자해도 어떻게 연습하느냐가 중요합니다. 편안한 수준에서 반복하는 것이 아니라 끊임없이 도전하는 연습이어야 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>Câu hỏi phụ 1 — q_text: 남자의 중심 생각으로 맞는 것을 고르십시오.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>Đáp án:</t>
+          <t>Câu hỏi phụ 1 — q_text: 남자의 중심 생각으로 맞는 것을 고르십시오.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>① 어떤 분야든지 만 시간을 투자하면 전문성이 쌓인다. (trap_shared_noun — "만 시간", "전문성" nhưng thiếu điều kiện quan trọng)</t>
+          <t>Đáp án:</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>② 전문가가 되려면 한계를 극복하려는 노력이 필요하다. ✅ (đúng — "한계를 넘어서려는 의식적인 노력")</t>
+          <t>① 어떤 분야든지 만 시간을 투자하면 전문성이 쌓인다. (trap_shared_noun — "만 시간", "전문성" nhưng thiếu điều kiện quan trọng)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>③ 성공의 기본 조건은 충분한 시간 투자이다. (trap_shared_noun — "기본 조건", "시간 투자" nhưng bỏ qua ý chính)</t>
+          <t>② 전문가가 되려면 한계를 극복하려는 노력이 필요하다. ✅ (đúng — "한계를 넘어서려는 의식적인 노력")</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>④ 편안한 수준에서 반복 연습하는 것이 효과적이다. (trap_shared_noun + trap_neg_않못 — "편안한 수준에서 반복" nhưng 남자 nói ngược lại)</t>
+          <t>③ 성공의 기본 조건은 충분한 시간 투자이다. (trap_shared_noun — "기본 조건", "시간 투자" nhưng bỏ qua ý chính)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>Đúng: ②</t>
+          <t>④ 편안한 수준에서 반복 연습하는 것이 효과적이다. (trap_shared_noun + trap_neg_않못 — "편안한 수준에서 반복" nhưng 남자 nói ngược lại)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>Câu hỏi phụ 2 — q_text: 들은 내용과 일치하는 것을 고르십시오.</t>
+          <t>Đúng: ②</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>Đáp án:</t>
+          <t>Câu hỏi phụ 2 — q_text: 들은 내용과 일치하는 것을 고르십시오.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>① 남자는 시간 투자만으로 전문가가 될 수 있다고 했다. (trap_shared_noun + trap_neg_않못 — 실제로는 "시간만 채우는 것이 아니라")</t>
+          <t>Đáp án:</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>② '1만 시간의 법칙'은 아직 대중에게 알려지지 않았다. (trap_shared_noun + trap_neg_않못 — "화제를 모으고 있는데" → 반대)</t>
+          <t>① 남자는 시간 투자만으로 전문가가 될 수 있다고 했다. (trap_shared_noun + trap_neg_않못 — 실제로는 "시간만 채우는 것이 아니라")</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>③ 남자에 따르면 연습의 질이 시간의 양보다 중요하다. ✅ (đúng — "어떻게 연습하느냐가 중요")</t>
+          <t>② '1만 시간의 법칙'은 아직 대중에게 알려지지 않았다. (trap_shared_noun + trap_neg_않못 — "화제를 모으고 있는데" → 반대)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>④ 여자는 시간 투자만으로 충분하다는 입장이다. (trap_shared_noun + trap_subject_swap — 여자는 질문했을 뿐, 이 입장 아님)</t>
+          <t>③ 남자에 따르면 연습의 질이 시간의 양보다 중요하다. ✅ (đúng — "어떻게 연습하느냐가 중요")</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
+          <t>④ 여자는 시간 투자만으로 충분하다는 입장이다. (trap_shared_noun + trap_subject_swap — 여자는 질문했을 뿐, 이 입장 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
           <t>Đúng: ③</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="13" t="inlineStr">
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="13" t="inlineStr">
         <is>
           <t>JSON mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "kind": 210007,</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "title": "다음은 대담입니다. 잘 듣고 물음에 답하십시오.",</t>
+          <t xml:space="preserve">  "kind": 210007,</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "audio": "여자: 박사님이 저술하신 '1만 시간의 법칙'이 요즘 화제를 모으고 있는데요, 아직 읽어 보지 않은 분들을 위해 소개 좀 해 주시겠습니까?\n남자: '1만 시간의 법칙'은 어떤 분야든 만 시간을 투자해야 전문성이 쌓이고 성공할 수 있는 기본 조건이 갖춰진다는 법칙입니다. 하지만 단순히 시간만 채우는 것이 아니라 자신의 한계를 넘어서려는 의식적인 노력이 필요합니다.\n여자: 그렇다면 시간 투자만으로는 부족하다는 말씀이신가요?\n남자: 네, 맞습니다. 같은 시간을 투자해도 어떻게 연습하느냐가 중요합니다. 편안한 수준에서 반복하는 것이 아니라 끊임없이 도전하는 연습이어야 합니다.",</t>
+          <t xml:space="preserve">  "title": "다음은 대담입니다. 잘 듣고 물음에 답하십시오.",</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "contents": [</t>
+          <t xml:space="preserve">  "audio": "여자: 박사님이 저술하신 '1만 시간의 법칙'이 요즘 화제를 모으고 있는데요, 아직 읽어 보지 않은 분들을 위해 소개 좀 해 주시겠습니까?\n남자: '1만 시간의 법칙'은 어떤 분야든 만 시간을 투자해야 전문성이 쌓이고 성공할 수 있는 기본 조건이 갖춰진다는 법칙입니다. 하지만 단순히 시간만 채우는 것이 아니라 자신의 한계를 넘어서려는 의식적인 노력이 필요합니다.\n여자: 그렇다면 시간 투자만으로는 부족하다는 말씀이신가요?\n남자: 네, 맞습니다. 같은 시간을 투자해도 어떻게 연습하느냐가 중요합니다. 편안한 수준에서 반복하는 것이 아니라 끊임없이 도전하는 연습이어야 합니다.",</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {</t>
+          <t xml:space="preserve">  "contents": [</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "남자의 중심 생각으로 맞는 것을 고르십시오.",</t>
+          <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "answers": [</t>
+          <t xml:space="preserve">      "q_text": "남자의 중심 생각으로 맞는 것을 고르십시오.",</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "어떤 분야든지 만 시간을 투자하면 전문성이 쌓인다.",</t>
+          <t xml:space="preserve">      "answers": [</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "전문가가 되려면 한계를 극복하려는 노력이 필요하다.",</t>
+          <t xml:space="preserve">        "어떤 분야든지 만 시간을 투자하면 전문성이 쌓인다.",</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "성공의 기본 조건은 충분한 시간 투자이다.",</t>
+          <t xml:space="preserve">        "전문가가 되려면 한계를 극복하려는 노력이 필요하다.",</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "편안한 수준에서 반복 연습하는 것이 효과적이다."</t>
+          <t xml:space="preserve">        "성공의 기본 조건은 충분한 시간 투자이다.",</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ],</t>
+          <t xml:space="preserve">        "편안한 수준에서 반복 연습하는 것이 효과적이다."</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "correct": 2</t>
+          <t xml:space="preserve">      ],</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "correct": 2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {</t>
+          <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "들은 내용과 일치하는 것을 고르십시오.",</t>
+          <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "answers": [</t>
+          <t xml:space="preserve">      "q_text": "들은 내용과 일치하는 것을 고르십시오.",</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "남자는 시간 투자만으로 전문가가 될 수 있다고 했다.",</t>
+          <t xml:space="preserve">      "answers": [</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "'1만 시간의 법칙'은 아직 대중에게 알려지지 않았다.",</t>
+          <t xml:space="preserve">        "남자는 시간 투자만으로 전문가가 될 수 있다고 했다.",</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "남자에 따르면 연습의 질이 시간의 양보다 중요하다.",</t>
+          <t xml:space="preserve">        "'1만 시간의 법칙'은 아직 대중에게 알려지지 않았다.",</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "여자는 시간 투자만으로 충분하다는 입장이다."</t>
+          <t xml:space="preserve">        "남자에 따르면 연습의 질이 시간의 양보다 중요하다.",</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ],</t>
+          <t xml:space="preserve">        "여자는 시간 투자만으로 충분하다는 입장이다."</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "correct": 3</t>
+          <t xml:space="preserve">      ],</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    }</t>
+          <t xml:space="preserve">      "correct": 3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ]</t>
+          <t xml:space="preserve">    }</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A118:F118"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A3:F3"/>
@@ -14033,7 +14244,6 @@
     <mergeCell ref="A99:F99"/>
     <mergeCell ref="A108:F108"/>
     <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A62:F62"/>
@@ -14041,6 +14251,7 @@
     <mergeCell ref="A125:F125"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A127:F127"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A114:F114"/>
     <mergeCell ref="A59:F59"/>
@@ -14049,16 +14260,17 @@
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A88:F88"/>
     <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A90:F90"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A105:F105"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A71:F71"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A116:F116"/>
     <mergeCell ref="A100:F100"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="A115:F115"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A102:F102"/>
@@ -14068,7 +14280,6 @@
     <mergeCell ref="A92:F92"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="A78:F78"/>
@@ -14085,7 +14296,6 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A96:F96"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A123:F123"/>
     <mergeCell ref="A110:F110"/>
@@ -15352,7 +15562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15767,49 +15977,77 @@
       <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Không có bẫy rõ — đáp án là danh từ địa điểm đơn lẻ, không phải câu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc audio</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>`trap_shared_noun`</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án sai chứa từ vựng liên quan đến audio nhưng sai địa điểm</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>• Hội thoại ngắn giữa 남자/여자 (2 lượt nói)</t>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>`trap_similar_word`</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án là địa điểm phát âm tương tự (e.g. 약국↔학교)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>• Gợi ý địa điểm qua từ khóa ngữ cảnh (KHÔNG nói thẳng tên địa điểm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>• Format: 남자: ...\n여자: ... hoặc 여자: ...\n남자: ...</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án là nơi được nhắc tới nhưng không phải nơi được hỏi</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Cấu trúc đáp án</t>
+          <t>Cấu trúc audio</t>
         </is>
       </c>
       <c r="B44" s="10" t="n"/>
@@ -15821,28 +16059,28 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>• 4 tên địa điểm (danh từ đơn)</t>
+          <t>• Hội thoại ngắn giữa 남자/여자 (2 lượt nói)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
+          <t>• Gợi ý địa điểm qua từ khóa ngữ cảnh (KHÔNG nói thẳng tên địa điểm)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: địa điểm được gợi ý bởi từ khóa trong hội thoại</t>
+          <t>• Format: 남자: ...\n여자: ... hoặc 여자: ...\n남자: ...</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Ngân hàng địa điểm (Place Bank)</t>
+          <t>Cấu trúc đáp án</t>
         </is>
       </c>
       <c r="B48" s="10" t="n"/>
@@ -15854,706 +16092,738 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
+          <t>• 4 tên địa điểm (danh từ đơn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>• q_text: rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án đúng: địa điểm được gợi ý bởi từ khóa trong hội thoại</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Ngân hàng địa điểm (Place Bank)</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
           <t>Xếp theo tần suất xuất hiện:</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>Tiếng Hàn</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>Tần suất</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>Từ khóa ngữ cảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>`bank`</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>은행</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>돈, 통장, 계좌, 환전</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>`post_office`</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>우체국</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>편지, 소포, 우표, 보내다</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>`pharmacy`</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>약국</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>약, 감기약, 처방전</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>`restaurant`</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>식당</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>주문, 메뉴, 음식, 맛</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>`department_store`</t>
+          <t>`bank`</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>백화점</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>옷, 쇼핑, 할인, 층</t>
+          <t>돈, 통장, 계좌, 환전</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>`theater`</t>
+          <t>`post_office`</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>극장</t>
+          <t>우체국</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>영화, 표, 좌석, 상영</t>
+          <t>편지, 소포, 우표, 보내다</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>`library`</t>
+          <t>`pharmacy`</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>도서관</t>
+          <t>약국</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>책, 빌리다, 반납, 조용히</t>
+          <t>약, 감기약, 처방전</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>`bookstore`</t>
+          <t>`restaurant`</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>서점</t>
+          <t>식당</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>책, 사다, 베스트셀러</t>
+          <t>주문, 메뉴, 음식, 맛</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>`park`</t>
+          <t>`department_store`</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>공원</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>산책, 운동, 꽃, 벤치</t>
+          <t>옷, 쇼핑, 할인, 층</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>`market`</t>
+          <t>`theater`</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>시장</t>
+          <t>극장</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>채소, 과일, 싸다, 얼마</t>
+          <t>영화, 표, 좌석, 상영</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>`hospital`</t>
+          <t>`library`</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>병원</t>
+          <t>도서관</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>아프다, 의사, 진찰, 주사</t>
+          <t>책, 빌리다, 반납, 조용히</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>`airport`</t>
+          <t>`bookstore`</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>공항</t>
+          <t>서점</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>비행기, 여권, 출발, 탑승</t>
+          <t>책, 사다, 베스트셀러</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>`school`</t>
+          <t>`park`</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>학교</t>
+          <t>공원</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>수업, 선생님, 학생</t>
+          <t>산책, 운동, 꽃, 벤치</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>`classroom`</t>
+          <t>`market`</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>교실</t>
+          <t>시장</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>수업, 칠판, 선생님</t>
+          <t>채소, 과일, 싸다, 얼마</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>`company`</t>
+          <t>`hospital`</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>회사</t>
+          <t>병원</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>회의, 보고서, 출근</t>
+          <t>아프다, 의사, 진찰, 주사</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>`flower_shop`</t>
+          <t>`airport`</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>꽃집</t>
+          <t>공항</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>꽃, 장미, 선물</t>
+          <t>비행기, 여권, 출발, 탑승</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>`playground`</t>
+          <t>`school`</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>운동장</t>
+          <t>학교</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>축구, 달리기, 운동</t>
+          <t>수업, 선생님, 학생</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>`travel_agency`</t>
+          <t>`classroom`</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>여행사</t>
+          <t>교실</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>여행, 예약, 비행기</t>
+          <t>수업, 칠판, 선생님</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>`photo_studio`</t>
+          <t>`company`</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>사진관</t>
+          <t>회사</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>사진, 찍다, 증명사진</t>
+          <t>회의, 보고서, 출근</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>`bakery`</t>
+          <t>`flower_shop`</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>빵집</t>
+          <t>꽃집</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>빵, 케이크, 맛있다</t>
+          <t>꽃, 장미, 선물</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>`hair_salon`</t>
+          <t>`playground`</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>운동장</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>머리, 자르다, 파마</t>
+          <t>축구, 달리기, 운동</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>`museum`</t>
+          <t>`travel_agency`</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>박물관</t>
+          <t>여행사</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>전시, 작품, 관람</t>
+          <t>여행, 예약, 비행기</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>`store`</t>
+          <t>`photo_studio`</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>가게</t>
+          <t>사진관</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>물건, 사다, 팔다</t>
+          <t>사진, 찍다, 증명사진</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>`hotel`</t>
+          <t>`bakery`</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>호텔</t>
+          <t>빵집</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>방, 예약, 체크인</t>
+          <t>빵, 케이크, 맛있다</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>`cinema`</t>
+          <t>`hair_salon`</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>영화관</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>영화, 표, 팝콘</t>
+          <t>머리, 자르다, 파마</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>`art_museum`</t>
+          <t>`museum`</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>미술관</t>
+          <t>박물관</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>그림, 전시, 작품</t>
+          <t>전시, 작품, 관람</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>`taxi`</t>
+          <t>`store`</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>택시</t>
+          <t>가게</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>타다, 기사, 요금</t>
+          <t>물건, 사다, 팔다</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
+          <t>`hotel`</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>호텔</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>방, 예약, 체크인</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>`cinema`</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>영화관</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>영화, 표, 팝콘</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>`art_museum`</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>미술관</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>그림, 전시, 작품</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>`taxi`</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>택시</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>타다, 기사, 요금</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
           <t>`train_station`</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>기차역</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>기차, 표, 출발</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B80" s="10" t="n"/>
-      <c r="C80" s="10" t="n"/>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="10" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>Audio: 남자: 뭘 드릴까요?\n여자: 아침부터 머리가 아파요. 약 좀 주세요.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="11" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>Đáp án: ① 병원 ② 약국 ③ 식당 ④ 학교</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>Đúng: ② 약국 (từ khóa "약 좀 주세요" gợi ý nhà thuốc)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="22">
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A87:F87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16565,7 +16835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16980,75 +17250,103 @@
       <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Không có bẫy rõ — đáp án là danh từ chủ đề đơn lẻ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>`trap_shared_noun`</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án sai chứa từ vựng xuất hiện trong audio nhưng sai chủ đề chính</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>`trap_partial_topic`</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án chỉ đề cập một phần nội dung, không phải chủ đề chính</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>`trap_similar_word`</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Chủ đề phát âm/nghĩa gần nhưng khác nội dung (e.g. 운동↔운전)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>• Hội thoại ngắn giữa 남자/여자 về một chủ đề cụ thể (2 lượt thoại)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>• Format: 남자: ...\n여자: ... hoặc 여자: ...\n남자: ...</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc đáp án</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>• 4 danh từ trừu tượng chỉ chủ đề</t>
-        </is>
-      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
+          <t>• Hội thoại ngắn giữa 남자/여자 về một chủ đề cụ thể (2 lượt thoại)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: chủ đề được gợi ý bởi từ khóa trong hội thoại</t>
+          <t>• Format: 남자: ...\n여자: ... hoặc 여자: ...\n남자: ...</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Ngân hàng danh từ chủ đề (Topic Noun Bank)</t>
+          <t>Cấu trúc đáp án</t>
         </is>
       </c>
       <c r="B47" s="10" t="n"/>
@@ -17058,661 +17356,693 @@
       <c r="F47" s="10" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>• 4 danh từ trừu tượng chỉ chủ đề</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>• q_text: rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>• Đáp án đúng: chủ đề được gợi ý bởi từ khóa trong hội thoại</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Ngân hàng danh từ chủ đề (Topic Noun Bank)</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>Tiếng Hàn</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>Tần suất</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>Từ khóa ngữ cảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>`hobby`</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>취미</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>좋아하다, 영화, 노래, 운동</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>`time`</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>시간</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>몇 시, 오전, 오후, 늦다</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>`weather`</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>날씨</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>비, 눈, 덥다, 춥다</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>`appointment`</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>약속</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>만나다, 장소, 시간</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>`date`</t>
+          <t>`hobby`</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>날짜</t>
+          <t>취미</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>며칠, 월, 일</t>
+          <t>좋아하다, 영화, 노래, 운동</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>`weekend`</t>
+          <t>`time`</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>주말</t>
+          <t>시간</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>토요일, 일요일, 쉬다</t>
+          <t>몇 시, 오전, 오후, 늦다</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>`travel`</t>
+          <t>`weather`</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>여행</t>
+          <t>날씨</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>가다, 어디, 비행기</t>
+          <t>비, 눈, 덥다, 춥다</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>`season`</t>
+          <t>`appointment`</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>계절</t>
+          <t>약속</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>봄, 여름, 가을, 겨울</t>
+          <t>만나다, 장소, 시간</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>`exercise`</t>
+          <t>`date`</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>운동</t>
+          <t>날짜</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>축구, 수영, 건강</t>
+          <t>며칠, 월, 일</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>`day_of_week`</t>
+          <t>`weekend`</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>요일</t>
+          <t>주말</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>월요일~일요일</t>
+          <t>토요일, 일요일, 쉬다</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>`plan`</t>
+          <t>`travel`</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>여행</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>하다, 방학, 휴가</t>
+          <t>가다, 어디, 비행기</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>`job`</t>
+          <t>`season`</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>계절</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>일하다, 회사, 되다</t>
+          <t>봄, 여름, 가을, 겨울</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>`country`</t>
+          <t>`exercise`</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>나라</t>
+          <t>운동</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>한국, 중국, 일본</t>
+          <t>축구, 수영, 건강</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>`gift`</t>
+          <t>`day_of_week`</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>선물</t>
+          <t>요일</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>주다, 받다, 생일</t>
+          <t>월요일~일요일</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>`age`</t>
+          <t>`plan`</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>나이</t>
+          <t>계획</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>몇 살, 젊다, 많다</t>
+          <t>하다, 방학, 휴가</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>`holiday`</t>
+          <t>`job`</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>휴일</t>
+          <t>직업</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>쉬다, 놀다, 연휴</t>
+          <t>일하다, 회사, 되다</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>`food`</t>
+          <t>`country`</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>음식</t>
+          <t>나라</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>먹다, 맛, 요리하다</t>
+          <t>한국, 중국, 일본</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>`mood`</t>
+          <t>`gift`</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>기분</t>
+          <t>선물</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>좋다, 나쁘다, 기쁘다</t>
+          <t>주다, 받다, 생일</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>`place`</t>
+          <t>`age`</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>장소</t>
+          <t>나이</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>어디, 여기, 거기</t>
+          <t>몇 살, 젊다, 많다</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>`family`</t>
+          <t>`holiday`</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>가족</t>
+          <t>휴일</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>엄마, 아빠, 형제</t>
+          <t>쉬다, 놀다, 연휴</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>`hometown`</t>
+          <t>`food`</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>고향</t>
+          <t>음식</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>어디, 나라, 도시</t>
+          <t>먹다, 맛, 요리하다</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>`address`</t>
+          <t>`mood`</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>기분</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>어디, 살다, 번지</t>
+          <t>좋다, 나쁘다, 기쁘다</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>`name`</t>
+          <t>`place`</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>장소</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>뭐, 누구, 부르다</t>
+          <t>어디, 여기, 거기</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>`price`</t>
+          <t>`family`</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>가족</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>얼마, 비싸다, 싸다</t>
+          <t>엄마, 아빠, 형제</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>`birthday`</t>
+          <t>`hometown`</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>생일</t>
+          <t>고향</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>선물, 파티, 축하</t>
+          <t>어디, 나라, 도시</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>`health`</t>
+          <t>`address`</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>건강</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>아프다, 운동, 병원</t>
+          <t>어디, 살다, 번지</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
+          <t>`name`</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>뭐, 누구, 부르다</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>`price`</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>얼마, 비싸다, 싸다</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>`birthday`</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>생일</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>선물, 파티, 축하</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>`health`</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>건강</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>아프다, 운동, 병원</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
           <t>`taste`</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>맛있다, 달다, 맵다</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="10" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>Audio: Hội thoại nhắc "비싸요", "천 원" → Đúng: 값</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A41:F41"/>
+  <mergeCells count="18">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A81:F81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
